--- a/excel/dashboard_financiero.xlsx
+++ b/excel/dashboard_financiero.xlsx
@@ -20,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#.##0,00 &quot;ARS&quot;"/>
+    <numFmt numFmtId="165" formatCode="#.##0,00 &quot;USD&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -347,7 +347,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Flujo_Caja'!I1</f>
+              <f>'Flujo_Caja'!K1</f>
             </strRef>
           </tx>
           <spPr>
@@ -362,7 +362,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Flujo_Caja'!$I$2:$I$25</f>
+              <f>'Flujo_Caja'!$K$2:$K$25</f>
             </numRef>
           </val>
         </ser>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,36 +758,36 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ingresos último mes (ARS)</t>
+          <t>Ingresos último mes</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>$109,183,526</t>
+          <t>ARS 115,6 M (USD 76,3 k)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EBITDA último mes (ARS)</t>
+          <t>EBITDA último mes</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>$23,272,294</t>
+          <t>ARS 26,7 M (USD 17,6 k)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Resultado neto último mes (ARS)</t>
+          <t>Resultado neto último mes</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>$16,061,666</t>
+          <t>ARS 19,2 M (USD 12,7 k)</t>
         </is>
       </c>
     </row>
@@ -799,19 +799,31 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Flujo neto último mes (ARS)</t>
+          <t>Flujo neto último mes</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>$-62,999,060</t>
+          <t>ARS 3,5 M (USD 2,3 k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Saldo de caja</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ARS 357,4 M (USD 236,0 k)</t>
         </is>
       </c>
     </row>
@@ -1049,64 +1061,64 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>89657237.48999999</v>
+        <v>93456965.23</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>59196.67</v>
+        <v>61705.46</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>49340289.04</v>
+        <v>52392158.75</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>32577.19</v>
+        <v>34592.2</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>40316948.45</v>
+        <v>41064806.48</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>26619.48</v>
+        <v>27113.26</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>19867340.75</v>
+        <v>25563356.04</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>13117.52</v>
+        <v>16878.34</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>20449607.7</v>
+        <v>15501450.44</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>13501.96</v>
+        <v>10234.92</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>1344858.56</v>
+        <v>1401854.48</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>887.95</v>
+        <v>925.58</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>19104749.14</v>
+        <v>14099595.96</v>
       </c>
       <c r="P3" s="8" t="n">
-        <v>12614.01</v>
+        <v>9309.33</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>-719342.16</v>
+        <v>-958982.79</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>-474.95</v>
+        <v>-633.17</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>4776187.28</v>
+        <v>3524898.99</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>3153.5</v>
+        <v>2327.33</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>15047904.01</v>
+        <v>11533679.77</v>
       </c>
       <c r="V3" s="8" t="n">
-        <v>9935.459999999999</v>
+        <v>7615.17</v>
       </c>
     </row>
     <row r="4">
@@ -1121,64 +1133,64 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>99589794.61</v>
+        <v>96604256.11</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>65754.7</v>
+        <v>63783.48</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>55958346.74</v>
+        <v>50406925.47</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>36946.8</v>
+        <v>33281.44</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>43631447.88</v>
+        <v>46197330.64</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>28807.9</v>
+        <v>30502.04</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>23942883.56</v>
+        <v>22520217.88</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>15808.42</v>
+        <v>14869.09</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>19688564.32</v>
+        <v>23677112.76</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>12999.48</v>
+        <v>15632.94</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>1493846.92</v>
+        <v>1449063.84</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>986.3200000000001</v>
+        <v>956.75</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>18194717.4</v>
+        <v>22228048.92</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>12013.16</v>
+        <v>14676.19</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>-885394.11</v>
+        <v>-182861.64</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>-584.59</v>
+        <v>-120.74</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>4548679.35</v>
+        <v>5557012.23</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>3003.29</v>
+        <v>3669.05</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>14531432.16</v>
+        <v>16853898.33</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>9594.459999999999</v>
+        <v>11127.88</v>
       </c>
     </row>
     <row r="5">
@@ -1193,64 +1205,64 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>102806199.73</v>
+        <v>96540179.23</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>67878.35000000001</v>
+        <v>63741.17</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>57960480.97</v>
+        <v>51352642.55</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>38268.72</v>
+        <v>33905.86</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>44845718.76</v>
+        <v>45187536.69</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>29609.63</v>
+        <v>29835.31</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>25925018.28</v>
+        <v>25003237.04</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>17117.13</v>
+        <v>16508.52</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>18920700.49</v>
+        <v>20184299.65</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>12492.49</v>
+        <v>13326.79</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>1542093</v>
+        <v>1448102.69</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>1018.18</v>
+        <v>956.12</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>17378607.49</v>
+        <v>18736196.96</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>11474.32</v>
+        <v>12370.67</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>767172.28</v>
+        <v>-106307.19</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>506.53</v>
+        <v>-70.19</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>4344651.87</v>
+        <v>4684049.24</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>2868.58</v>
+        <v>3092.67</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>12266783.34</v>
+        <v>14158454.91</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>8099.21</v>
+        <v>9348.200000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1265,64 +1277,64 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>102235689.95</v>
+        <v>98339809.84</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>67501.66</v>
+        <v>64929.39</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>53443652.02</v>
+        <v>54613597.64</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>35286.46</v>
+        <v>36058.92</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>48792037.93</v>
+        <v>43726212.21</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>32215.2</v>
+        <v>28870.47</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>23889812.04</v>
+        <v>26410712.4</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>15773.38</v>
+        <v>17437.81</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>24902225.89</v>
+        <v>17315499.81</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>16441.83</v>
+        <v>11432.65</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>1533535.35</v>
+        <v>1475097.15</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>1012.52</v>
+        <v>973.9400000000001</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>23368690.54</v>
+        <v>15840402.66</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>15429.3</v>
+        <v>10458.71</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>-635112.72</v>
+        <v>-1167295.98</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>-419.34</v>
+        <v>-770.71</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>5842172.64</v>
+        <v>3960100.67</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>3857.33</v>
+        <v>2614.68</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>18161630.62</v>
+        <v>13047597.98</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>11991.31</v>
+        <v>8614.75</v>
       </c>
     </row>
     <row r="7">
@@ -1337,64 +1349,64 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>97189048.20999999</v>
+        <v>100611736.23</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>64169.59</v>
+        <v>66429.44</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>51760012.4</v>
+        <v>56532563.84</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>34174.83</v>
+        <v>37325.93</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>45429035.81</v>
+        <v>44079172.39</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>29994.76</v>
+        <v>29103.51</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>22938429.83</v>
+        <v>24188573.68</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>15145.22</v>
+        <v>15970.64</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>22490605.97</v>
+        <v>19890598.71</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>14849.54</v>
+        <v>13132.87</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>1457835.72</v>
+        <v>1509176.04</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>962.54</v>
+        <v>996.4400000000001</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>21032770.25</v>
+        <v>18381422.66</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>13887</v>
+        <v>12136.43</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>654382.78</v>
+        <v>-894479.59</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>432.06</v>
+        <v>-590.58</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>5258192.56</v>
+        <v>4595355.67</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>3471.75</v>
+        <v>3034.11</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>15120194.91</v>
+        <v>14680546.58</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>9983.190000000001</v>
+        <v>9692.91</v>
       </c>
     </row>
     <row r="8">
@@ -1409,64 +1421,64 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>97868264.73</v>
+        <v>97624826.17</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>64618.05</v>
+        <v>64457.32</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>54649637.62</v>
+        <v>52736508.65</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>36082.72</v>
+        <v>34819.56</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>43218627.12</v>
+        <v>44888317.52</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>28535.33</v>
+        <v>29637.75</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>24801480.54</v>
+        <v>22020719.57</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>16375.31</v>
+        <v>14539.3</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18417146.58</v>
+        <v>22867597.96</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>12160.02</v>
+        <v>15098.45</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>1468023.97</v>
+        <v>1464372.39</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>969.27</v>
+        <v>966.86</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>16949122.61</v>
+        <v>21403225.56</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>11190.75</v>
+        <v>14131.59</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>165621</v>
+        <v>-982659.52</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>109.35</v>
+        <v>-648.8099999999999</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>4237280.65</v>
+        <v>5350806.39</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>2797.69</v>
+        <v>3532.9</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>12546220.96</v>
+        <v>17035078.7</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>8283.709999999999</v>
+        <v>11247.5</v>
       </c>
     </row>
     <row r="9">
@@ -1481,64 +1493,64 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>87887230.23</v>
+        <v>92468453.17</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>58028.02</v>
+        <v>61052.79</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>50673543.11</v>
+        <v>51433132.39</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>33457.48</v>
+        <v>33959</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>37213687.12</v>
+        <v>41035320.79</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>24570.54</v>
+        <v>27093.79</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>23956482.05</v>
+        <v>24821093.87</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>15817.4</v>
+        <v>16388.26</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>13257205.07</v>
+        <v>16214226.91</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>8753.139999999999</v>
+        <v>10705.53</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>1318308.45</v>
+        <v>1387026.8</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>870.42</v>
+        <v>915.79</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>11938896.62</v>
+        <v>14827200.12</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>7882.72</v>
+        <v>9789.74</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>-501523.42</v>
+        <v>239921.95</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>-331.13</v>
+        <v>158.41</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>2984724.15</v>
+        <v>3706800.03</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>1970.68</v>
+        <v>2447.43</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>9455695.880000001</v>
+        <v>10880478.13</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>6243.17</v>
+        <v>7183.89</v>
       </c>
     </row>
     <row r="10">
@@ -1553,64 +1565,64 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>87562305.41</v>
+        <v>87387060.17</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>57813.48</v>
+        <v>57697.78</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>46912774.47</v>
+        <v>50543534.83</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>30974.41</v>
+        <v>33371.64</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>40649530.94</v>
+        <v>36843525.33</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>26839.07</v>
+        <v>24326.14</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>22334969.01</v>
+        <v>21209893.62</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>14746.78</v>
+        <v>14003.95</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>18314561.93</v>
+        <v>15633631.71</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>12092.29</v>
+        <v>10322.19</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>1313434.58</v>
+        <v>1310805.9</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>867.2</v>
+        <v>865.47</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>17001127.35</v>
+        <v>14322825.81</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>11225.09</v>
+        <v>9456.719999999999</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>521561.17</v>
+        <v>-83820.56</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>344.36</v>
+        <v>-55.34</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>4250281.84</v>
+        <v>3580706.45</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>2806.27</v>
+        <v>2364.18</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>12229284.34</v>
+        <v>10825939.92</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>8074.45</v>
+        <v>7147.88</v>
       </c>
     </row>
     <row r="11">
@@ -1625,64 +1637,64 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>84203331.14</v>
+        <v>89208085.03</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>55595.7</v>
+        <v>58900.12</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>46955715</v>
+        <v>49698821.97</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>31002.76</v>
+        <v>32813.91</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>37247616.14</v>
+        <v>39509263.05</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>24592.94</v>
+        <v>26086.2</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>22526476.11</v>
+        <v>24238052.05</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>14873.23</v>
+        <v>16003.3</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>14721140.03</v>
+        <v>15271211</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>9719.709999999999</v>
+        <v>10082.9</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>1263049.97</v>
+        <v>1338121.28</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>833.9400000000001</v>
+        <v>883.5</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>13458090.06</v>
+        <v>13933089.73</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>8885.780000000001</v>
+        <v>9199.4</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>-299494.46</v>
+        <v>-40407.44</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>-197.74</v>
+        <v>-26.68</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>3364522.51</v>
+        <v>3483272.43</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>2221.44</v>
+        <v>2299.85</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>10393062.01</v>
+        <v>10490224.73</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>6862.07</v>
+        <v>6926.23</v>
       </c>
     </row>
     <row r="12">
@@ -1697,64 +1709,64 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>86364007.45</v>
+        <v>91347414.59</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>57022.3</v>
+        <v>60312.62</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>48643949.35</v>
+        <v>47751811.92</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>32117.43</v>
+        <v>31528.39</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>37720058.1</v>
+        <v>43595602.66</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>24904.87</v>
+        <v>28784.23</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>22532596</v>
+        <v>21345506.31</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>14877.27</v>
+        <v>14093.49</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>15187462.1</v>
+        <v>22250096.36</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>10027.6</v>
+        <v>14690.75</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>1295460.11</v>
+        <v>1370211.22</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>855.33</v>
+        <v>904.6900000000001</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>13892001.99</v>
+        <v>20879885.14</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>9172.27</v>
+        <v>13786.06</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>-108869.9</v>
+        <v>-567472.13</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>-71.88</v>
+        <v>-374.68</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>3473000.5</v>
+        <v>5219971.28</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>2293.07</v>
+        <v>3446.51</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>10527871.39</v>
+        <v>16227385.98</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>6951.08</v>
+        <v>10714.22</v>
       </c>
     </row>
     <row r="13">
@@ -1769,64 +1781,64 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>98598337.48999999</v>
+        <v>92502408.31999999</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>65100.08</v>
+        <v>61075.21</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>52829318.85</v>
+        <v>49393275.38</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>34880.84</v>
+        <v>32612.18</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>45769018.64</v>
+        <v>43109132.94</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>30219.24</v>
+        <v>28463.04</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>24653051.76</v>
+        <v>20911102.36</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>16277.31</v>
+        <v>13806.67</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>21115966.89</v>
+        <v>22198030.58</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>13941.93</v>
+        <v>14656.37</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>1478975.06</v>
+        <v>1387536.12</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>976.5</v>
+        <v>916.13</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>19636991.82</v>
+        <v>20810494.45</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>12965.43</v>
+        <v>13740.24</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>-830884.48</v>
+        <v>-595764.35</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>-548.6</v>
+        <v>-393.36</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>4909247.96</v>
+        <v>5202623.61</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>3241.36</v>
+        <v>3435.06</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>15558628.35</v>
+        <v>16203635.18</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>10272.67</v>
+        <v>10698.54</v>
       </c>
     </row>
     <row r="14">
@@ -1841,64 +1853,64 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>105530649.3</v>
+        <v>104481947.53</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>69677.17999999999</v>
+        <v>68984.77</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>58291198.79</v>
+        <v>56617715.31</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>38487.08</v>
+        <v>37382.15</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>47239450.51</v>
+        <v>47864232.22</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>31190.1</v>
+        <v>31602.62</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>28146880.32</v>
+        <v>25306662.16</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>18584.13</v>
+        <v>16708.86</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>19092570.19</v>
+        <v>22557570.06</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>12605.97</v>
+        <v>14893.76</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>1582959.74</v>
+        <v>1567229.21</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>1045.16</v>
+        <v>1034.77</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>17509610.45</v>
+        <v>20990340.85</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>11560.81</v>
+        <v>13858.99</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>-146996.44</v>
+        <v>-815989.3199999999</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>-97.06</v>
+        <v>-538.76</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>4377402.61</v>
+        <v>5247585.21</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>2890.2</v>
+        <v>3464.75</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>13279204.28</v>
+        <v>16558744.95</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>8767.67</v>
+        <v>10933</v>
       </c>
     </row>
     <row r="15">
@@ -1913,64 +1925,64 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>109471301.28</v>
+        <v>109110744.16</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>72279.00999999999</v>
+        <v>72040.95</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>57305545.27</v>
+        <v>62869531.71</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>37836.29</v>
+        <v>41509.95</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>52165756.01</v>
+        <v>46241212.45</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>34442.72</v>
+        <v>30531.01</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>29850697.48</v>
+        <v>28246821.1</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>19709.08</v>
+        <v>18650.12</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>22315058.53</v>
+        <v>17994391.35</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>14733.64</v>
+        <v>11880.89</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1642069.52</v>
+        <v>1636661.16</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>1084.19</v>
+        <v>1080.61</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>20672989.01</v>
+        <v>16357730.19</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>13649.45</v>
+        <v>10800.28</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>759620.15</v>
+        <v>19925.82</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>501.54</v>
+        <v>13.16</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>5168247.25</v>
+        <v>4089432.55</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>3412.36</v>
+        <v>2700.07</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>14745121.61</v>
+        <v>12248371.82</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>9735.549999999999</v>
+        <v>8087.05</v>
       </c>
     </row>
     <row r="16">
@@ -1985,64 +1997,64 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>117247185.73</v>
+        <v>114388733.68</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>77413.08</v>
+        <v>75525.78</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>64836312.02</v>
+        <v>64486374.98</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>42808.52</v>
+        <v>42577.48</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>52410873.71</v>
+        <v>49902358.7</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>34604.56</v>
+        <v>32948.3</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>27659009.49</v>
+        <v>26287005.67</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>18262.01</v>
+        <v>17356.14</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>24751864.22</v>
+        <v>23615353.03</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>16342.55</v>
+        <v>15592.16</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>1758707.79</v>
+        <v>1715831.01</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>1161.2</v>
+        <v>1132.89</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>22993156.43</v>
+        <v>21899522.03</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>15181.35</v>
+        <v>14459.28</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>638840.15</v>
+        <v>-504556.25</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>421.8</v>
+        <v>-333.14</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>5748289.11</v>
+        <v>5474880.51</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>3795.34</v>
+        <v>3614.82</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>16606027.18</v>
+        <v>16929197.77</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>10964.22</v>
+        <v>11177.59</v>
       </c>
     </row>
     <row r="17">
@@ -2057,64 +2069,64 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>125693243.03</v>
+        <v>125638826.49</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>82989.64</v>
+        <v>82953.71000000001</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>70261603.20999999</v>
+        <v>70156718.90000001</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>46390.6</v>
+        <v>46321.35</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>55431639.81</v>
+        <v>55482107.59</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>36599.04</v>
+        <v>36632.36</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>30956486.68</v>
+        <v>31839012.56</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>20439.19</v>
+        <v>21021.88</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>24475153.13</v>
+        <v>23643095.03</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>16159.85</v>
+        <v>15610.48</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>1885398.65</v>
+        <v>1884582.4</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>1244.84</v>
+        <v>1244.31</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>22589754.48</v>
+        <v>21758512.63</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>14915.01</v>
+        <v>14366.17</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>-207203.2</v>
+        <v>212616.7</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>-136.81</v>
+        <v>140.38</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>5647438.62</v>
+        <v>5439628.16</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>3728.75</v>
+        <v>3591.54</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>17149519.06</v>
+        <v>16106267.77</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>11323.06</v>
+        <v>10634.25</v>
       </c>
     </row>
     <row r="18">
@@ -2129,64 +2141,64 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>116709599.26</v>
+        <v>124172393.29</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>77058.14</v>
+        <v>81985.49000000001</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>65108338.01</v>
+        <v>70351110.48</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>42988.13</v>
+        <v>46449.7</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>51601261.25</v>
+        <v>53821282.81</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>34070.01</v>
+        <v>35535.79</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>27279294.07</v>
+        <v>29024413.36</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>18011.3</v>
+        <v>19163.52</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>24321967.18</v>
+        <v>24796869.45</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>16058.71</v>
+        <v>16372.27</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>1750643.99</v>
+        <v>1862585.9</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>1155.87</v>
+        <v>1229.78</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>22571323.19</v>
+        <v>22934283.55</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>14902.84</v>
+        <v>15142.48</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>712908.95</v>
+        <v>-1410349.44</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>470.7</v>
+        <v>-931.1900000000001</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>5642830.8</v>
+        <v>5733570.89</v>
       </c>
       <c r="T18" s="8" t="n">
-        <v>3725.71</v>
+        <v>3785.62</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>16215583.45</v>
+        <v>18611062.1</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>10706.43</v>
+        <v>12288.05</v>
       </c>
     </row>
     <row r="19">
@@ -2201,64 +2213,64 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>121770377.76</v>
+        <v>115933339.95</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>80399.55</v>
+        <v>76545.61</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>67492764.43000001</v>
+        <v>62147742.42</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>44562.46</v>
+        <v>41033.38</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>54277613.33</v>
+        <v>53785597.54</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>35837.09</v>
+        <v>35512.23</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>30242922.87</v>
+        <v>26972931.53</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>19968.05</v>
+        <v>17809.02</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>24034690.46</v>
+        <v>26812666</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>15869.03</v>
+        <v>17703.21</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>1826555.67</v>
+        <v>1739000.1</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>1205.99</v>
+        <v>1148.18</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>22208134.79</v>
+        <v>25073665.91</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>14663.04</v>
+        <v>16555.02</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>449623.54</v>
+        <v>795093.37</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>296.87</v>
+        <v>524.96</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>5552033.7</v>
+        <v>6268416.48</v>
       </c>
       <c r="T19" s="8" t="n">
-        <v>3665.76</v>
+        <v>4138.76</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>16206477.55</v>
+        <v>18010156.06</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>10700.41</v>
+        <v>11891.3</v>
       </c>
     </row>
     <row r="20">
@@ -2273,64 +2285,64 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>114602415.69</v>
+        <v>115928513.01</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>75666.86</v>
+        <v>76542.42</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>64223408.38</v>
+        <v>62471635.1</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>42403.85</v>
+        <v>41247.23</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>50379007.3</v>
+        <v>53456877.92</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>33263.01</v>
+        <v>35295.19</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>31979794.09</v>
+        <v>30063314.65</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>21114.83</v>
+        <v>19849.46</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>18399213.21</v>
+        <v>23393563.27</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>12148.18</v>
+        <v>15445.73</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>1719036.24</v>
+        <v>1738927.7</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>1135</v>
+        <v>1148.14</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>16680176.98</v>
+        <v>21654635.57</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>11013.18</v>
+        <v>14297.59</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>-1149650.47</v>
+        <v>-473841.8</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>-759.0599999999999</v>
+        <v>-312.86</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>4170044.24</v>
+        <v>5413658.89</v>
       </c>
       <c r="T20" s="8" t="n">
-        <v>2753.29</v>
+        <v>3574.4</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>13659783.21</v>
+        <v>16714818.47</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>9018.950000000001</v>
+        <v>11036.05</v>
       </c>
     </row>
     <row r="21">
@@ -2345,64 +2357,64 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>106555695.71</v>
+        <v>110781815.76</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>70353.97</v>
+        <v>73144.28999999999</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>57189796.07</v>
+        <v>60656490.68</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>37759.87</v>
+        <v>40048.77</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>49365899.64</v>
+        <v>50125325.08</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>32594.1</v>
+        <v>33095.51</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>25039351.05</v>
+        <v>26132633.81</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>16532.37</v>
+        <v>17254.21</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>24326548.59</v>
+        <v>23992691.26</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>16061.73</v>
+        <v>15841.3</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>1598335.44</v>
+        <v>1661727.24</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>1055.31</v>
+        <v>1097.16</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>22728213.16</v>
+        <v>22330964.03</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>15006.42</v>
+        <v>14744.14</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>688915.8199999999</v>
+        <v>-782944.9300000001</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>454.86</v>
+        <v>-516.9400000000001</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>5682053.29</v>
+        <v>5582741.01</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>3751.61</v>
+        <v>3686.03</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>16357244.05</v>
+        <v>17531167.95</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>10799.96</v>
+        <v>11575.05</v>
       </c>
     </row>
     <row r="22">
@@ -2417,64 +2429,64 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>107473029.9</v>
+        <v>104095048.4</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>70959.64</v>
+        <v>68729.31</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>61859543.53</v>
+        <v>55770431.19</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>40843.1</v>
+        <v>36822.73</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>45613486.36</v>
+        <v>48324617.2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>30116.55</v>
+        <v>31906.59</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>29116780.7</v>
+        <v>26552061.06</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>19224.51</v>
+        <v>17531.14</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>16496705.66</v>
+        <v>21772556.14</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>10892.04</v>
+        <v>14375.45</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>1612095.45</v>
+        <v>1561425.73</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>1064.39</v>
+        <v>1030.94</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>14884610.21</v>
+        <v>20211130.41</v>
       </c>
       <c r="P22" s="8" t="n">
-        <v>9827.639999999999</v>
+        <v>13344.51</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>-932197.1800000001</v>
+        <v>620037.75</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>-615.49</v>
+        <v>409.38</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>3721152.55</v>
+        <v>5052782.6</v>
       </c>
       <c r="T22" s="8" t="n">
-        <v>2456.91</v>
+        <v>3336.13</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>12095654.84</v>
+        <v>14538310.06</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>7986.22</v>
+        <v>9599</v>
       </c>
     </row>
     <row r="23">
@@ -2489,64 +2501,64 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>101138275.69</v>
+        <v>102244861.39</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>66777.09</v>
+        <v>67507.72</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>57349876.28</v>
+        <v>54512793.16</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>37865.56</v>
+        <v>35992.36</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>43788399.41</v>
+        <v>47732068.23</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>28911.53</v>
+        <v>31515.35</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>25011546.35</v>
+        <v>28613455.17</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>16514.01</v>
+        <v>18892.19</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>18776853.06</v>
+        <v>19118613.07</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>12397.52</v>
+        <v>12623.17</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>1517074.14</v>
+        <v>1533672.92</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>1001.66</v>
+        <v>1012.62</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>17259778.92</v>
+        <v>17584940.15</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>11395.86</v>
+        <v>11610.55</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>-358014.35</v>
+        <v>-185009.43</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>-236.38</v>
+        <v>-122.15</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>4314944.73</v>
+        <v>4396235.04</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>2848.97</v>
+        <v>2902.64</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>13302848.54</v>
+        <v>13373714.54</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>8783.280000000001</v>
+        <v>8830.07</v>
       </c>
     </row>
     <row r="24">
@@ -2561,64 +2573,64 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>110315463.83</v>
+        <v>102848652.28</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>72836.38</v>
+        <v>67906.37</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>61197593.74</v>
+        <v>53772050.53</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>40406.04</v>
+        <v>35503.28</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>49117870.09</v>
+        <v>49076601.75</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>32430.34</v>
+        <v>32403.09</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>27858152.95</v>
+        <v>23303339.42</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>18393.49</v>
+        <v>15386.15</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>21259717.14</v>
+        <v>25773262.33</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>14036.84</v>
+        <v>17016.93</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>1654731.96</v>
+        <v>1542729.78</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>1092.55</v>
+        <v>1018.6</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>19604985.19</v>
+        <v>24230532.55</v>
       </c>
       <c r="P24" s="8" t="n">
-        <v>12944.3</v>
+        <v>15998.34</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>326479.85</v>
+        <v>56455.77</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>215.56</v>
+        <v>37.28</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>4901246.3</v>
+        <v>6057633.14</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>3236.07</v>
+        <v>3999.58</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>14377259.04</v>
+        <v>18116443.64</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>9492.66</v>
+        <v>11961.48</v>
       </c>
     </row>
     <row r="25">
@@ -2633,64 +2645,64 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>109183526.49</v>
+        <v>115618497.41</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>72089.00999999999</v>
+        <v>76337.73</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>57992775.25</v>
+        <v>63050188.72</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>38290.04</v>
+        <v>41629.23</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>51190751.24</v>
+        <v>52568308.7</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>33798.97</v>
+        <v>34708.51</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>27918457.71</v>
+        <v>25876768.11</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>18433.31</v>
+        <v>17085.28</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>23272293.54</v>
+        <v>26691540.59</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>15365.66</v>
+        <v>17623.23</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>1637752.9</v>
+        <v>1734277.46</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>1081.34</v>
+        <v>1145.07</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>21634540.64</v>
+        <v>24957263.13</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>14284.32</v>
+        <v>16478.17</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>164239.44</v>
+        <v>-504977</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>108.44</v>
+        <v>-333.41</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>5408635.16</v>
+        <v>6239315.78</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>3571.08</v>
+        <v>4119.54</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>16061666.04</v>
+        <v>19222924.35</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>10604.8</v>
+        <v>12692.04</v>
       </c>
     </row>
   </sheetData>
@@ -2705,7 +2717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2718,6 +2730,10 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2743,32 +2759,52 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>variacion_ct_ars</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>variacion_ct_usd</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>inversiones_ars</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>inversiones_usd</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>flujo_financiero_ars</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>flujo_financiero_usd</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>flujo_neto_ars</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>flujo_neto_usd</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>saldo_caja_ars</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>saldo_caja_usd</t>
         </is>
       </c>
     </row>
@@ -2784,28 +2820,40 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>-39912730.91</v>
+        <v>16569417.38</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>-26352.59</v>
+        <v>10940.05</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>659217.54</v>
+        <v>-0</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>435.25</v>
+        <v>-0</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>647686.4399999999</v>
+        <v>-704359.9399999999</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>427.64</v>
+        <v>-465.06</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>-38605826.93</v>
+        <v>492475.45</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>-25489.7</v>
+        <v>325.16</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>16357532.89</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>10800.15</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>58357532.89</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>38530.87</v>
       </c>
     </row>
     <row r="3">
@@ -2820,28 +2868,40 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>-44165171.05</v>
+        <v>13391023.24</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>-29160.29</v>
+        <v>8841.49</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-493639.47</v>
+        <v>455488.99</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>-325.93</v>
+        <v>300.74</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>719342.16</v>
+        <v>-2139183.2</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>474.95</v>
+        <v>-1412.41</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>-43939468.37</v>
+        <v>509885.9</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>-29011.27</v>
+        <v>336.65</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>11761725.93</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>7765.74</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>70119258.81999999</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>46296.62</v>
       </c>
     </row>
     <row r="4">
@@ -2856,28 +2916,40 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>-53931521.74</v>
+        <v>15722884.7</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>-35608.58</v>
+        <v>10381.12</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>-2623249.52</v>
+        <v>-2580077.47</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>-1732.01</v>
+        <v>-1703.51</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>885394.11</v>
+        <v>-2025084.46</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>584.59</v>
+        <v>-1337.07</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>-55669377.15</v>
+        <v>122460.52</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>-36756.01</v>
+        <v>80.86</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>13820260.77</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>9124.9</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>83939519.59</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>55421.52</v>
       </c>
     </row>
     <row r="5">
@@ -2892,28 +2964,40 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>-59338849.61</v>
+        <v>17199715.22</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>-39178.79</v>
+        <v>11356.2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-493052.04</v>
+        <v>1593157.62</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-325.54</v>
+        <v>1051.89</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-767172.28</v>
+        <v>-1277008.4</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-506.53</v>
+        <v>-843.15</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-60599073.92</v>
+        <v>6072016.05</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>-40010.86</v>
+        <v>4009.08</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>21994722.87</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>14522.13</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>105934242.46</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>69943.64999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2928,28 +3012,40 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-48825602.66</v>
+        <v>13903528.75</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>-32237.37</v>
+        <v>9179.879999999999</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>-3754187.71</v>
+        <v>-619166.38</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-2478.72</v>
+        <v>-408.81</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>635112.72</v>
+        <v>-1581284.52</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>419.34</v>
+        <v>-1044.05</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-51944677.65</v>
+        <v>787810.15</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>-34296.75</v>
+        <v>520.16</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>13110054.39</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>8655.98</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>119044296.85</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>78599.64</v>
       </c>
     </row>
     <row r="7">
@@ -2964,28 +3060,40 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-47230543.73</v>
+        <v>10141635.67</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>-31184.22</v>
+        <v>6696.07</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>88743.37</v>
+        <v>-6048086.95</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>58.59</v>
+        <v>-3993.28</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-654382.78</v>
+        <v>-11942912.66</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-432.06</v>
+        <v>-7885.37</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-47796183.14</v>
+        <v>802862.23</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>-31557.69</v>
+        <v>530.09</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>-998414.76</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>-659.21</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>118045882.09</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>77940.42999999999</v>
       </c>
     </row>
     <row r="8">
@@ -3000,28 +3108,40 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>-54896102.16</v>
+        <v>24869178.15</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>-36245.45</v>
+        <v>16420.01</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1722480.59</v>
+        <v>6369727.06</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1137.28</v>
+        <v>4205.65</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-165621</v>
+        <v>-1146476.24</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-109.35</v>
+        <v>-756.97</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-53339242.56</v>
+        <v>427944.82</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>-35217.52</v>
+        <v>282.55</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>24150646.74</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>15945.59</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>142196528.83</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>93886.02</v>
       </c>
     </row>
     <row r="9">
@@ -3036,28 +3156,40 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-55563811.08</v>
+        <v>15815462</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>-36686.3</v>
+        <v>10442.24</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-1796134.62</v>
+        <v>3547957.07</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1185.91</v>
+        <v>2342.56</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>501523.42</v>
+        <v>-947737.05</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>331.13</v>
+        <v>-625.75</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>-56858422.28</v>
+        <v>-6293904.77</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>-37541.08</v>
+        <v>-4155.58</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>8573820.189999999</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>5660.91</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>150770349.01</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>99546.92999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3072,28 +3204,40 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>-46515663.08</v>
+        <v>13004559.73</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>-30712.22</v>
+        <v>8586.33</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>-3333315.2</v>
+        <v>867813.91</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-2200.84</v>
+        <v>572.98</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-521561.17</v>
+        <v>-1392899</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-344.36</v>
+        <v>-919.67</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-50370539.44</v>
+        <v>64084</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>-33257.42</v>
+        <v>42.31</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>11675744.73</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>7708.97</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>162446093.74</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>107255.91</v>
       </c>
     </row>
     <row r="11">
@@ -3108,28 +3252,40 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-50416067.73</v>
+        <v>6496513.06</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>-33287.48</v>
+        <v>4289.36</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-1838838.35</v>
+        <v>-5331832.95</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1214.1</v>
+        <v>-3520.37</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>299494.46</v>
+        <v>-1394003.92</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>197.74</v>
+        <v>-920.4</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>-51955411.62</v>
+        <v>24686.55</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>-34303.84</v>
+        <v>16.3</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>5127195.69</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>3385.26</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>167573289.43</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>110641.16</v>
       </c>
     </row>
     <row r="12">
@@ -3144,28 +3300,40 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>-51266535.35</v>
+        <v>14330189.81</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>-33849.01</v>
+        <v>9461.58</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>353762.51</v>
+        <v>-3267407.39</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>233.57</v>
+        <v>-2157.32</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>108869.9</v>
+        <v>-2029051.61</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>71.88</v>
+        <v>-1339.69</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-50803902.95</v>
+        <v>501928.04</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>-33543.55</v>
+        <v>331.4</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>12803066.24</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>8453.290000000001</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>180376355.67</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>119094.46</v>
       </c>
     </row>
     <row r="13">
@@ -3180,28 +3348,40 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-50421985.11</v>
+        <v>21308592.43</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>-33291.39</v>
+        <v>14069.11</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2667268.12</v>
+        <v>3717421.13</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>1761.08</v>
+        <v>2454.45</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>830884.48</v>
+        <v>-2289457.76</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>548.6</v>
+        <v>-1511.63</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-46923832.5</v>
+        <v>317305</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>-30981.71</v>
+        <v>209.5</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>19336439.67</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>12766.99</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>199712795.35</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>131861.44</v>
       </c>
     </row>
     <row r="14">
@@ -3216,28 +3396,40 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-62167381.01</v>
+        <v>10898497.31</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>-41046.35</v>
+        <v>7195.79</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>-2910999.04</v>
+        <v>-7227476.85</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-1922</v>
+        <v>-4771.98</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>146996.44</v>
+        <v>-1362865.97</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>97.06</v>
+        <v>-899.84</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-64931383.61</v>
+        <v>721623.98</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>-42871.29</v>
+        <v>476.46</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>10257255.31</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>6772.41</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>209970050.66</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>138633.85</v>
       </c>
     </row>
     <row r="15">
@@ -3252,28 +3444,40 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>-59830779.5</v>
+        <v>15815008.24</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>-39503.59</v>
+        <v>10441.94</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-1248077.23</v>
+        <v>1929975.26</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-824.05</v>
+        <v>1274.28</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-759620.15</v>
+        <v>-2655018.07</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>-501.54</v>
+        <v>-1752.99</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-61838476.88</v>
+        <v>-8768.469999999999</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>-40829.19</v>
+        <v>-5.79</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>13151221.7</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>8683.16</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>223121272.36</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>147317.02</v>
       </c>
     </row>
     <row r="16">
@@ -3288,28 +3492,40 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>-61902905.54</v>
+        <v>14623249.06</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>-40871.73</v>
+        <v>9655.08</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>-4551556.79</v>
+        <v>-4021779.72</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-3005.19</v>
+        <v>-2655.4</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>-638840.15</v>
+        <v>-15519250.96</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>-421.8</v>
+        <v>-10246.67</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-67093302.48</v>
+        <v>10405837.35</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>-44298.71</v>
+        <v>6870.51</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>9509835.449999999</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>6278.92</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>232631107.81</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>153595.94</v>
       </c>
     </row>
     <row r="17">
@@ -3324,28 +3540,40 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>-70782343.45</v>
+        <v>13868365.99</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>-46734.42</v>
+        <v>9156.66</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-4717300.88</v>
+        <v>-4122484.18</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-3114.62</v>
+        <v>-2721.89</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>207203.2</v>
+        <v>-2439746.93</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>136.81</v>
+        <v>-1610.86</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-75292441.14</v>
+        <v>-116938.87</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>-49712.24</v>
+        <v>-77.20999999999999</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>11311680.19</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>7468.6</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>243942788</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>161064.54</v>
       </c>
     </row>
     <row r="18">
@@ -3360,28 +3588,40 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>-61140975.24</v>
+        <v>12625830.83</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>-40368.66</v>
+        <v>8336.27</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>-6175602.66</v>
+        <v>-7847817.17</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-4077.47</v>
+        <v>-5181.56</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>-712908.95</v>
+        <v>-1553198.84</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>-470.7</v>
+        <v>-1025.51</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-68029486.84999999</v>
+        <v>1222250.7</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>-44916.83</v>
+        <v>807</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>12294882.68</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>8117.76</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>256237670.69</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>169182.3</v>
       </c>
     </row>
     <row r="19">
@@ -3396,28 +3636,40 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-66336834.47</v>
+        <v>28928239.51</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>-43799.25</v>
+        <v>19100.03</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-4987593.95</v>
+        <v>9179083.35</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-3293.09</v>
+        <v>6060.54</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-449623.54</v>
+        <v>-2216366.92</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>-296.87</v>
+        <v>-1463.37</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-71774051.95999999</v>
+        <v>-321147.4</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>-47389.2</v>
+        <v>-212.04</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>26390725.19</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>17424.62</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>282628395.88</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>186606.92</v>
       </c>
     </row>
     <row r="20">
@@ -3432,28 +3684,40 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>-70847631.8</v>
+        <v>23748753.84</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>-46777.53</v>
+        <v>15680.24</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>-2987655.12</v>
+        <v>5295007.67</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-1972.62</v>
+        <v>3496.06</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>1149650.47</v>
+        <v>-1464167.8</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>759.0599999999999</v>
+        <v>-966.72</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-72685636.45</v>
+        <v>332833.55</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>-47991.08</v>
+        <v>219.76</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>22617419.59</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>14933.27</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>305245815.47</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>201540.19</v>
       </c>
     </row>
     <row r="21">
@@ -3468,28 +3732,40 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>-52893690.84</v>
+        <v>18517414.01</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>-34923.34</v>
+        <v>12226.22</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2784823.57</v>
+        <v>-675481.1800000001</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1838.69</v>
+        <v>-445.99</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-688915.8199999999</v>
+        <v>-5839007.43</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>-454.86</v>
+        <v>-3855.24</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-50797783.09</v>
+        <v>421490.66</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>-33539.51</v>
+        <v>278.29</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>13099897.24</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>8649.280000000001</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>318345712.71</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>210189.47</v>
       </c>
     </row>
     <row r="22">
@@ -3504,28 +3780,40 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>-67710199.38</v>
+        <v>16797198.22</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>-44706.02</v>
+        <v>11090.44</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-4151174.81</v>
+        <v>697462.4300000001</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-2740.84</v>
+        <v>460.5</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>932197.1800000001</v>
+        <v>-4398777.33</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>615.49</v>
+        <v>-2904.32</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-70929177.01000001</v>
+        <v>-6921612.02</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>-46831.37</v>
+        <v>-4570.03</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>5476808.86</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>3616.09</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>323822521.58</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>213805.56</v>
       </c>
     </row>
     <row r="23">
@@ -3540,28 +3828,40 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>-57014180.6</v>
+        <v>20622894.01</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>-37643.92</v>
+        <v>13616.38</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>3999236.9</v>
+        <v>5715506.55</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>2640.52</v>
+        <v>3773.69</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>358014.35</v>
+        <v>-2201748.94</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>236.38</v>
+        <v>-1453.72</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-52656929.35</v>
+        <v>153622.82</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>-34767.02</v>
+        <v>101.43</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>18574767.88</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>12264.09</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>342397289.46</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>226069.65</v>
       </c>
     </row>
     <row r="24">
@@ -3576,28 +3876,40 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>-62624669.51</v>
+        <v>12650850.43</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>-41348.27</v>
+        <v>8352.790000000001</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-174545.6</v>
+        <v>-7008322.99</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-115.24</v>
+        <v>-4627.28</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>-326479.85</v>
+        <v>-1093014.46</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>-215.56</v>
+        <v>-721.67</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>-63125694.96</v>
+        <v>-48830.88</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>-41679.08</v>
+        <v>-32.24</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>11509005.08</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>7598.88</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>353906294.54</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>233668.53</v>
       </c>
     </row>
     <row r="25">
@@ -3612,28 +3924,40 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-57592773.1</v>
+        <v>21133380.14</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>-38025.94</v>
+        <v>13953.43</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-5242047.26</v>
+        <v>176178.33</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-3461.09</v>
+        <v>116.32</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-164239.44</v>
+        <v>-18019021.79</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>-108.44</v>
+        <v>-11897.16</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-62999059.8</v>
+        <v>404545.95</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>-41595.47</v>
+        <v>267.1</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>3518904.3</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>2323.38</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>357425198.85</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>235991.91</v>
       </c>
     </row>
   </sheetData>
@@ -3726,10 +4050,10 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>89318811.19</v>
+        <v>87509868.37</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>58973.22</v>
+        <v>57778.86</v>
       </c>
       <c r="F2" s="7" t="n">
         <v>85948102.23</v>
@@ -3738,10 +4062,10 @@
         <v>56747.7</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>-3370708.96</v>
+        <v>-1561766.14</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>-3.77</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="3">
@@ -3761,10 +4085,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>42970568.39</v>
+        <v>44987699.16</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>28371.55</v>
+        <v>29703.37</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>44821990.78</v>
@@ -3773,10 +4097,10 @@
         <v>29593.96</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1851422.38</v>
+        <v>-165708.38</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.31</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="4">
@@ -3796,10 +4120,10 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>20168168.81</v>
+        <v>19852905.79</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>13316.14</v>
+        <v>13107.99</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>20326877.37</v>
@@ -3808,10 +4132,10 @@
         <v>13420.93</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>158708.56</v>
+        <v>473971.58</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>0.79</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="5">
@@ -3831,10 +4155,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>19821248.31</v>
+        <v>21092423.82</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>13087.09</v>
+        <v>13926.39</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>20799234.08</v>
@@ -3843,10 +4167,10 @@
         <v>13732.81</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>977985.77</v>
+        <v>-293189.74</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>4.93</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="6">
@@ -3866,22 +4190,22 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>87150785.33</v>
+        <v>93462442.86</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>57541.77</v>
+        <v>61709.08</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>89657237.48999999</v>
+        <v>93456965.23</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>59196.67</v>
+        <v>61705.46</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>2506452.15</v>
+        <v>-5477.63</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>2.88</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="7">
@@ -3901,22 +4225,22 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>49780728.5</v>
+        <v>50708546.58</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>32867.99</v>
+        <v>33480.59</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>49340289.04</v>
+        <v>52392158.75</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>32577.19</v>
+        <v>34592.2</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-440439.46</v>
+        <v>1683612.17</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.88</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="8">
@@ -3936,22 +4260,22 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>20482096.78</v>
+        <v>26618171.28</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>13523.41</v>
+        <v>17574.79</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>19867340.75</v>
+        <v>25563356.04</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>13117.52</v>
+        <v>16878.34</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>-614756.03</v>
+        <v>-1054815.24</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>-3</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="9">
@@ -3971,22 +4295,22 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>19440417.02</v>
+        <v>16075807.96</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>12835.64</v>
+        <v>10614.14</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>20449607.7</v>
+        <v>15501450.44</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>13501.96</v>
+        <v>10234.92</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1009190.68</v>
+        <v>-574357.52</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>5.19</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="10">
@@ -4006,22 +4330,22 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>95533958.83</v>
+        <v>99295906.48</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>63076.81</v>
+        <v>65560.66</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>99589794.61</v>
+        <v>96604256.11</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>65754.7</v>
+        <v>63783.48</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>4055835.78</v>
+        <v>-2691650.37</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>4.25</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="11">
@@ -4041,22 +4365,22 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>53701638.25</v>
+        <v>50559929</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>35456.79</v>
+        <v>33382.46</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>55958346.74</v>
+        <v>50406925.47</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>36946.8</v>
+        <v>33281.44</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>2256708.48</v>
+        <v>-153003.53</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>4.2</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="12">
@@ -4076,22 +4400,22 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>24774885.27</v>
+        <v>21395494.91</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>16357.75</v>
+        <v>14126.49</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>23942883.56</v>
+        <v>22520217.88</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>15808.42</v>
+        <v>14869.09</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-832001.72</v>
+        <v>1124722.97</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>-3.36</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="13">
@@ -4111,22 +4435,22 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>19892785.98</v>
+        <v>23260765.07</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>13134.32</v>
+        <v>15358.04</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>19688564.32</v>
+        <v>23677112.76</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>12999.48</v>
+        <v>15632.94</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-204221.66</v>
+        <v>416347.69</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-1.03</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="14">
@@ -4146,22 +4470,22 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>106192683.9</v>
+        <v>100189490.68</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>70114.28999999999</v>
+        <v>66150.64999999999</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>102806199.73</v>
+        <v>96540179.23</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>67878.35000000001</v>
+        <v>63741.17</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-3386484.17</v>
+        <v>-3649311.45</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>-3.19</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="15">
@@ -4181,22 +4505,22 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>58647427.15</v>
+        <v>53647846.06</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>38722.28</v>
+        <v>35421.28</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>57960480.97</v>
+        <v>51352642.55</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>38268.72</v>
+        <v>33905.86</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-686946.1899999999</v>
+        <v>-2295203.51</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-1.17</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="16">
@@ -4216,22 +4540,22 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>26862744.08</v>
+        <v>23967236.54</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>17736.27</v>
+        <v>15824.5</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>25925018.28</v>
+        <v>25003237.04</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>17117.13</v>
+        <v>16508.52</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-937725.8</v>
+        <v>1036000.5</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>-3.49</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="17">
@@ -4251,22 +4575,22 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>19067056.16</v>
+        <v>20156022.38</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>12589.13</v>
+        <v>13308.12</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18920700.49</v>
+        <v>20184299.65</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>12492.49</v>
+        <v>13326.79</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-146355.68</v>
+        <v>28277.27</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-0.77</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="18">
@@ -4286,22 +4610,22 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>98156500.54000001</v>
+        <v>96029381.2</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>64808.36</v>
+        <v>63403.91</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>102235689.95</v>
+        <v>98339809.84</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>67501.66</v>
+        <v>64929.39</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>4079189.42</v>
+        <v>2310428.64</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>4.16</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="19">
@@ -4321,22 +4645,22 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>52257061.87</v>
+        <v>56647588.47</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>34503.01</v>
+        <v>37401.87</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>53443652.02</v>
+        <v>54613597.64</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>35286.46</v>
+        <v>36058.92</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>1186590.15</v>
+        <v>-2033990.83</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>2.27</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="20">
@@ -4356,22 +4680,22 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>24213959.62</v>
+        <v>26207714.22</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>15987.4</v>
+        <v>17303.78</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>23889812.04</v>
+        <v>26410712.4</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>15773.38</v>
+        <v>17437.81</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>-324147.59</v>
+        <v>202998.18</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>-1.34</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="21">
@@ -4391,22 +4715,22 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>24565627.93</v>
+        <v>16816464</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>16219.59</v>
+        <v>11103.16</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>24902225.89</v>
+        <v>17315499.81</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>16441.83</v>
+        <v>11432.65</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>336597.96</v>
+        <v>499035.81</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1.37</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="22">
@@ -4426,22 +4750,22 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>93992876.03</v>
+        <v>102119685.39</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>62059.3</v>
+        <v>67425.07000000001</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>97189048.20999999</v>
+        <v>100611736.23</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>64169.59</v>
+        <v>66429.44</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>3196172.18</v>
+        <v>-1507949.16</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>3.4</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="23">
@@ -4461,22 +4785,22 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>52945972.99</v>
+        <v>56182627.74</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>34957.86</v>
+        <v>37094.88</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>51760012.4</v>
+        <v>56532563.84</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>34174.83</v>
+        <v>37325.93</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-1185960.59</v>
+        <v>349936.1</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-2.24</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="24">
@@ -4496,22 +4820,22 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>22166328</v>
+        <v>24231087.13</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>14635.44</v>
+        <v>15998.71</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>22938429.83</v>
+        <v>24188573.68</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>15145.22</v>
+        <v>15970.64</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>772101.83</v>
+        <v>-42513.45</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>3.48</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="25">
@@ -4531,22 +4855,22 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>22219493.96</v>
+        <v>19136753.36</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>14670.54</v>
+        <v>12635.14</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>22490605.97</v>
+        <v>19890598.71</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>14849.54</v>
+        <v>13132.87</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>271112.02</v>
+        <v>753845.35</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>1.22</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="26">
@@ -4566,22 +4890,22 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>95216505.23</v>
+        <v>98904716.51000001</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>62867.21</v>
+        <v>65302.37</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>97868264.73</v>
+        <v>97624826.17</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>64618.05</v>
+        <v>64457.32</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>2651759.5</v>
+        <v>-1279890.34</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>2.78</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="27">
@@ -4601,22 +4925,22 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>52092582.41</v>
+        <v>51307042.25</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>34394.41</v>
+        <v>33875.75</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>54649637.62</v>
+        <v>52736508.65</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>36082.72</v>
+        <v>34819.56</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>2557055.21</v>
+        <v>1429466.4</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>4.91</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="28">
@@ -4636,22 +4960,22 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>24343776.78</v>
+        <v>22913483.61</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>16073.11</v>
+        <v>15128.75</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>24801480.54</v>
+        <v>22020719.57</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>16375.31</v>
+        <v>14539.3</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>457703.76</v>
+        <v>-892764.04</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>1.88</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="29">
@@ -4671,22 +4995,22 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>17989391.54</v>
+        <v>23689997.73</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>11877.59</v>
+        <v>15641.45</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>18417146.58</v>
+        <v>22867597.96</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>12160.02</v>
+        <v>15098.45</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>427755.03</v>
+        <v>-822399.77</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>2.38</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="30">
@@ -4706,22 +5030,22 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>91530574.18000001</v>
+        <v>93125377.66</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>60433.55</v>
+        <v>61486.53</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>87887230.23</v>
+        <v>92468453.17</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>58028.02</v>
+        <v>61052.79</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>-3643343.95</v>
+        <v>-656924.49</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>-3.98</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="31">
@@ -4741,22 +5065,22 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>50465030.87</v>
+        <v>51292570.92</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>33319.81</v>
+        <v>33866.2</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>50673543.11</v>
+        <v>51433132.39</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>33457.48</v>
+        <v>33959</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>208512.24</v>
+        <v>140561.47</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="32">
@@ -4776,22 +5100,22 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>23393217.64</v>
+        <v>25527550.41</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>15445.5</v>
+        <v>16854.7</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>23956482.05</v>
+        <v>24821093.87</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>15817.4</v>
+        <v>16388.26</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>563264.41</v>
+        <v>-706456.54</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>2.41</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="33">
@@ -4811,22 +5135,22 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>12921303.96</v>
+        <v>16712809.52</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>8531.360000000001</v>
+        <v>11034.72</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>13257205.07</v>
+        <v>16214226.91</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>8753.139999999999</v>
+        <v>10705.53</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>335901.11</v>
+        <v>-498582.61</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>2.6</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="34">
@@ -4846,22 +5170,22 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>91918859.40000001</v>
+        <v>88902041.98</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>60689.92</v>
+        <v>58698.05</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>87562305.41</v>
+        <v>87387060.17</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>57813.48</v>
+        <v>57697.78</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>-4356553.99</v>
+        <v>-1514981.81</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>-4.74</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="35">
@@ -4881,22 +5205,22 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>46957464.96</v>
+        <v>52990676.95</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>31003.92</v>
+        <v>34987.38</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>46912774.47</v>
+        <v>50543534.83</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>30974.41</v>
+        <v>33371.64</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>-44690.49</v>
+        <v>-2447142.12</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-0.1</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="36">
@@ -4916,22 +5240,22 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>21421266.45</v>
+        <v>20358142.2</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>14143.51</v>
+        <v>13441.57</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>22334969.01</v>
+        <v>21209893.62</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>14746.78</v>
+        <v>14003.95</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>913702.5600000001</v>
+        <v>851751.42</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>4.27</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="37">
@@ -4951,22 +5275,22 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>17485125.41</v>
+        <v>15481393.41</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>11544.65</v>
+        <v>10221.67</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>18314561.93</v>
+        <v>15633631.71</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>12092.29</v>
+        <v>10322.19</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>829436.52</v>
+        <v>152238.3</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>4.74</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="38">
@@ -4986,22 +5310,22 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>88380838.43000001</v>
+        <v>87232528.67</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>58353.92</v>
+        <v>57595.75</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>84203331.14</v>
+        <v>89208085.03</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>55595.7</v>
+        <v>58900.12</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>-4177507.29</v>
+        <v>1975556.36</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-4.73</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="39">
@@ -5021,22 +5345,22 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>47092423.49</v>
+        <v>48455389.49</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>31093.03</v>
+        <v>31992.93</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>46955715</v>
+        <v>49698821.97</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>31002.76</v>
+        <v>32813.91</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-136708.49</v>
+        <v>1243432.48</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-0.29</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="40">
@@ -5056,22 +5380,22 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>23587649.69</v>
+        <v>25263965.41</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>15573.87</v>
+        <v>16680.67</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>22526476.11</v>
+        <v>24238052.05</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>14873.23</v>
+        <v>16003.3</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>-1061173.58</v>
+        <v>-1025913.36</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-4.5</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="41">
@@ -5091,22 +5415,22 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>15252248.88</v>
+        <v>15184364.76</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>10070.38</v>
+        <v>10025.56</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>14721140.03</v>
+        <v>15271211</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>9719.709999999999</v>
+        <v>10082.9</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>-531108.85</v>
+        <v>86846.24000000001</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-3.48</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="42">
@@ -5126,22 +5450,22 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>83009216.36</v>
+        <v>95242166.75</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>54807.28</v>
+        <v>62884.15</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>86364007.45</v>
+        <v>91347414.59</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>57022.3</v>
+        <v>60312.62</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>3354791.1</v>
+        <v>-3894752.16</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>4.04</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="43">
@@ -5161,22 +5485,22 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>48326621.77</v>
+        <v>49416897.23</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>31907.91</v>
+        <v>32627.77</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>48643949.35</v>
+        <v>47751811.92</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>32117.43</v>
+        <v>31528.39</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>317327.58</v>
+        <v>-1665085.31</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>0.66</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="44">
@@ -5196,22 +5520,22 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>22428323.5</v>
+        <v>20633230.48</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>14808.42</v>
+        <v>13623.2</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>22532596</v>
+        <v>21345506.31</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>14877.27</v>
+        <v>14093.49</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>104272.5</v>
+        <v>712275.83</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>0.46</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="45">
@@ -5231,22 +5555,22 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>15876693.32</v>
+        <v>22218147.73</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>10482.67</v>
+        <v>14669.65</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>15187462.1</v>
+        <v>22250096.36</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>10027.6</v>
+        <v>14690.75</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>-689231.22</v>
+        <v>31948.63</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-4.34</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="46">
@@ -5266,22 +5590,22 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>96611036.64</v>
+        <v>95130129.8</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>63787.96</v>
+        <v>62810.18</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>98598337.48999999</v>
+        <v>92502408.31999999</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>65100.08</v>
+        <v>61075.21</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>1987300.85</v>
+        <v>-2627721.48</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>2.06</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="47">
@@ -5301,22 +5625,22 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>53563379.56</v>
+        <v>49171046.97</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>35365.51</v>
+        <v>32465.45</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>52829318.85</v>
+        <v>49393275.38</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>34880.84</v>
+        <v>32612.18</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-734060.72</v>
+        <v>222228.41</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-1.37</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="48">
@@ -5336,22 +5660,22 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>24921696.59</v>
+        <v>20750102.53</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>16454.68</v>
+        <v>13700.37</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>24653051.76</v>
+        <v>20911102.36</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>16277.31</v>
+        <v>13806.67</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>-268644.83</v>
+        <v>160999.83</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>-1.08</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="49">
@@ -5371,22 +5695,22 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>20382903.43</v>
+        <v>23213185.68</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>13457.92</v>
+        <v>15326.63</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>21115966.89</v>
+        <v>22198030.58</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>13941.93</v>
+        <v>14656.37</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>733063.45</v>
+        <v>-1015155.1</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>3.6</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="50">
@@ -5406,22 +5730,22 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>100459656.17</v>
+        <v>105309238.63</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>66329.03</v>
+        <v>69530.99000000001</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>105530649.3</v>
+        <v>104481947.53</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>69677.17999999999</v>
+        <v>68984.77</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>5070993.14</v>
+        <v>-827291.1</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>5.05</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="51">
@@ -5441,22 +5765,22 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>60792466.07</v>
+        <v>56856614.9</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>40138.55</v>
+        <v>37539.89</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>58291198.79</v>
+        <v>56617715.31</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>38487.08</v>
+        <v>37382.15</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-2501267.27</v>
+        <v>-238899.59</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-4.11</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="52">
@@ -5476,22 +5800,22 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>29212864.25</v>
+        <v>25934205.53</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>19287.95</v>
+        <v>17123.2</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>28146880.32</v>
+        <v>25306662.16</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>18584.13</v>
+        <v>16708.86</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>-1065983.94</v>
+        <v>-627543.37</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>-3.65</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="53">
@@ -5511,22 +5835,22 @@
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>19725804.93</v>
+        <v>21558642.52</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>13024.07</v>
+        <v>14234.21</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>19092570.19</v>
+        <v>22557570.06</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>12605.97</v>
+        <v>14893.76</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>-633234.74</v>
+        <v>998927.54</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-3.21</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="54">
@@ -5546,22 +5870,22 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>104755414.66</v>
+        <v>105682756.93</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>69165.32000000001</v>
+        <v>69777.61</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>109471301.28</v>
+        <v>109110744.16</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>72279.00999999999</v>
+        <v>72040.95</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>4715886.62</v>
+        <v>3427987.23</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>4.5</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="55">
@@ -5581,22 +5905,22 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>58798940.18</v>
+        <v>63467012.97</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>38822.32</v>
+        <v>41904.44</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>57305545.27</v>
+        <v>62869531.71</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>37836.29</v>
+        <v>41509.95</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>-1493394.92</v>
+        <v>-597481.26</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-2.54</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -5616,22 +5940,22 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>30644231.8</v>
+        <v>28741740.87</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>20233.02</v>
+        <v>18976.89</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>29850697.48</v>
+        <v>28246821.1</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>19709.08</v>
+        <v>18650.12</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>-793534.3100000001</v>
+        <v>-494919.77</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>-2.59</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="57">
@@ -5651,22 +5975,22 @@
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>21485811.91</v>
+        <v>17517906.88</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>14186.12</v>
+        <v>11566.29</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>22315058.53</v>
+        <v>17994391.35</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>14733.64</v>
+        <v>11880.89</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>829246.62</v>
+        <v>476484.47</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>3.86</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="58">
@@ -5686,22 +6010,22 @@
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>117707921.31</v>
+        <v>113464757.72</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>77717.28999999999</v>
+        <v>74915.72</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>117247185.73</v>
+        <v>114388733.68</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>77413.08</v>
+        <v>75525.78</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>-460735.58</v>
+        <v>923975.96</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>-0.39</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -5721,22 +6045,22 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>66327100.27</v>
+        <v>65025947.24</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>43792.82</v>
+        <v>42933.73</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>64836312.02</v>
+        <v>64486374.98</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>42808.52</v>
+        <v>42577.48</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>-1490788.25</v>
+        <v>-539572.26</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-2.25</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="60">
@@ -5756,22 +6080,22 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>26832422.93</v>
+        <v>26346894.61</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>17716.25</v>
+        <v>17395.68</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>27659009.49</v>
+        <v>26287005.67</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>18262.01</v>
+        <v>17356.14</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>826586.5600000001</v>
+        <v>-59888.94</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>3.08</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="61">
@@ -5791,22 +6115,22 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>24285826.94</v>
+        <v>24641927.2</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>16034.85</v>
+        <v>16269.96</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>24751864.22</v>
+        <v>23615353.03</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>16342.55</v>
+        <v>15592.16</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>466037.28</v>
+        <v>-1026574.17</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>1.92</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="62">
@@ -5826,22 +6150,22 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>123658087.95</v>
+        <v>123329298.36</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>81645.92</v>
+        <v>81428.83</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>125693243.03</v>
+        <v>125638826.49</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>82989.64</v>
+        <v>82953.71000000001</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>2035155.08</v>
+        <v>2309528.13</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="63">
@@ -5861,22 +6185,22 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>70882074.42</v>
+        <v>71923717.54000001</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>46800.27</v>
+        <v>47488.02</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>70261603.20999999</v>
+        <v>70156718.90000001</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>46390.6</v>
+        <v>46321.35</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-620471.21</v>
+        <v>-1766998.64</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-0.88</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="64">
@@ -5896,22 +6220,22 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>30121016.72</v>
+        <v>30478032.05</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>19887.56</v>
+        <v>20123.28</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>30956486.68</v>
+        <v>31839012.56</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>20439.19</v>
+        <v>21021.88</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>835469.97</v>
+        <v>1360980.51</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>2.77</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="65">
@@ -5931,22 +6255,22 @@
         </is>
       </c>
       <c r="D65" s="7" t="n">
-        <v>23790380.89</v>
+        <v>23544469.09</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>15707.73</v>
+        <v>15545.36</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>24475153.13</v>
+        <v>23643095.03</v>
       </c>
       <c r="G65" s="8" t="n">
-        <v>16159.85</v>
+        <v>15610.48</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>684772.24</v>
+        <v>98625.94</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>2.88</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="66">
@@ -5966,22 +6290,22 @@
         </is>
       </c>
       <c r="D66" s="7" t="n">
-        <v>113651861.84</v>
+        <v>128901674.89</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>75039.25</v>
+        <v>85108.02</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>116709599.26</v>
+        <v>124172393.29</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>77058.14</v>
+        <v>81985.49000000001</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>3057737.41</v>
+        <v>-4729281.6</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>2.69</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="67">
@@ -6001,22 +6325,22 @@
         </is>
       </c>
       <c r="D67" s="7" t="n">
-        <v>66208524.24</v>
+        <v>73019318.75</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>43714.53</v>
+        <v>48211.4</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>65108338.01</v>
+        <v>70351110.48</v>
       </c>
       <c r="G67" s="8" t="n">
-        <v>42988.13</v>
+        <v>46449.7</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>-1100186.23</v>
+        <v>-2668208.27</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-1.66</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="68">
@@ -6036,22 +6360,22 @@
         </is>
       </c>
       <c r="D68" s="7" t="n">
-        <v>26499752.25</v>
+        <v>28645723.39</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>17496.6</v>
+        <v>18913.49</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>27279294.07</v>
+        <v>29024413.36</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>18011.3</v>
+        <v>19163.52</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>779541.8199999999</v>
+        <v>378689.97</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>2.94</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="69">
@@ -6071,22 +6395,22 @@
         </is>
       </c>
       <c r="D69" s="7" t="n">
-        <v>23427677.27</v>
+        <v>23948188.74</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>15468.25</v>
+        <v>15811.92</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>24321967.18</v>
+        <v>24796869.45</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>16058.71</v>
+        <v>16372.27</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>894289.91</v>
+        <v>848680.71</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>3.82</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="70">
@@ -6106,22 +6430,22 @@
         </is>
       </c>
       <c r="D70" s="7" t="n">
-        <v>116862189.06</v>
+        <v>119609634.1</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>77158.89</v>
+        <v>78972.89999999999</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>121770377.76</v>
+        <v>115933339.95</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>80399.55</v>
+        <v>76545.61</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>4908188.7</v>
+        <v>-3676294.15</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>4.2</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="71">
@@ -6141,22 +6465,22 @@
         </is>
       </c>
       <c r="D71" s="7" t="n">
-        <v>67027409.8</v>
+        <v>60900926.66</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>44255.21</v>
+        <v>40210.16</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>67492764.43000001</v>
+        <v>62147742.42</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>44562.46</v>
+        <v>41033.38</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>465354.63</v>
+        <v>1246815.76</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="72">
@@ -6176,22 +6500,22 @@
         </is>
       </c>
       <c r="D72" s="7" t="n">
-        <v>30011802.29</v>
+        <v>27413638.79</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>19815.45</v>
+        <v>18100</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>30242922.87</v>
+        <v>26972931.53</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>19968.05</v>
+        <v>17809.02</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>231120.58</v>
+        <v>-440707.26</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>0.77</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="73">
@@ -6211,22 +6535,22 @@
         </is>
       </c>
       <c r="D73" s="7" t="n">
-        <v>23955435.27</v>
+        <v>27989554.36</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>15816.7</v>
+        <v>18480.25</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>24034690.46</v>
+        <v>26812666</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>15869.03</v>
+        <v>17703.21</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>79255.19</v>
+        <v>-1176888.36</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>0.33</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="74">
@@ -6246,22 +6570,22 @@
         </is>
       </c>
       <c r="D74" s="7" t="n">
-        <v>118747270.32</v>
+        <v>118451258.74</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>78403.52</v>
+        <v>78208.08</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>114602415.69</v>
+        <v>115928513.01</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>75666.86</v>
+        <v>76542.42</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>-4144854.64</v>
+        <v>-2522745.73</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>-3.49</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="75">
@@ -6281,22 +6605,22 @@
         </is>
       </c>
       <c r="D75" s="7" t="n">
-        <v>62609193.69</v>
+        <v>60619959.05</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>41338.06</v>
+        <v>40024.65</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>64223408.38</v>
+        <v>62471635.1</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>42403.85</v>
+        <v>41247.23</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>1614214.69</v>
+        <v>1851676.05</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="76">
@@ -6316,22 +6640,22 @@
         </is>
       </c>
       <c r="D76" s="7" t="n">
-        <v>30989088.56</v>
+        <v>30466878.45</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>20460.71</v>
+        <v>20115.92</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>31979794.09</v>
+        <v>30063314.65</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>21114.83</v>
+        <v>19849.46</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>990705.53</v>
+        <v>-403563.8</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>3.2</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="77">
@@ -6351,22 +6675,22 @@
         </is>
       </c>
       <c r="D77" s="7" t="n">
-        <v>18304666.18</v>
+        <v>22841437.52</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>12085.75</v>
+        <v>15081.18</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>18399213.21</v>
+        <v>23393563.27</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>12148.18</v>
+        <v>15445.73</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>94547.03</v>
+        <v>552125.75</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>0.52</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="78">
@@ -6386,22 +6710,22 @@
         </is>
       </c>
       <c r="D78" s="7" t="n">
-        <v>107091940.57</v>
+        <v>105282004.76</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>70708.03</v>
+        <v>69513.00999999999</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>106555695.71</v>
+        <v>110781815.76</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>70353.97</v>
+        <v>73144.28999999999</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>-536244.87</v>
+        <v>5499811</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>-0.5</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="79">
@@ -6421,22 +6745,22 @@
         </is>
       </c>
       <c r="D79" s="7" t="n">
-        <v>54619619.89</v>
+        <v>62301004.74</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>36062.9</v>
+        <v>41134.57</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>57189796.07</v>
+        <v>60656490.68</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>37759.87</v>
+        <v>40048.77</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>2570176.18</v>
+        <v>-1644514.06</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>4.71</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="80">
@@ -6456,22 +6780,22 @@
         </is>
       </c>
       <c r="D80" s="7" t="n">
-        <v>26289521.95</v>
+        <v>26490947.18</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>17357.8</v>
+        <v>17490.79</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>25039351.05</v>
+        <v>26132633.81</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>16532.37</v>
+        <v>17254.21</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>-1250170.9</v>
+        <v>-358313.37</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>-4.76</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="81">
@@ -6491,22 +6815,22 @@
         </is>
       </c>
       <c r="D81" s="7" t="n">
-        <v>25143987.73</v>
+        <v>23421557.87</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>16601.45</v>
+        <v>15464.21</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>24326548.59</v>
+        <v>23992691.26</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>16061.73</v>
+        <v>15841.3</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>-817439.14</v>
+        <v>571133.39</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-3.25</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="82">
@@ -6526,22 +6850,22 @@
         </is>
       </c>
       <c r="D82" s="7" t="n">
-        <v>106409479.94</v>
+        <v>108299744.82</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>70257.42999999999</v>
+        <v>71505.49000000001</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>107473029.9</v>
+        <v>104095048.4</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>70959.64</v>
+        <v>68729.31</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>1063549.96</v>
+        <v>-4204696.42</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>1</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="83">
@@ -6561,22 +6885,22 @@
         </is>
       </c>
       <c r="D83" s="7" t="n">
-        <v>59129282.27</v>
+        <v>56024690.2</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>39040.43</v>
+        <v>36990.6</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>61859543.53</v>
+        <v>55770431.19</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>40843.1</v>
+        <v>36822.73</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>2730261.27</v>
+        <v>-254259.01</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>4.62</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="84">
@@ -6596,22 +6920,22 @@
         </is>
       </c>
       <c r="D84" s="7" t="n">
-        <v>28764389.38</v>
+        <v>27440479.8</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>18991.84</v>
+        <v>18117.72</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>29116780.7</v>
+        <v>26552061.06</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>19224.51</v>
+        <v>17531.14</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>352391.32</v>
+        <v>-888418.74</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>1.23</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="85">
@@ -6631,22 +6955,22 @@
         </is>
       </c>
       <c r="D85" s="7" t="n">
-        <v>17297305.38</v>
+        <v>21952200.56</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>11420.64</v>
+        <v>14494.06</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>16496705.66</v>
+        <v>21772556.14</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>10892.04</v>
+        <v>14375.45</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>-800599.72</v>
+        <v>-179644.42</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-4.63</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="86">
@@ -6666,22 +6990,22 @@
         </is>
       </c>
       <c r="D86" s="7" t="n">
-        <v>101702306.89</v>
+        <v>106323660.81</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>67149.49000000001</v>
+        <v>70200.77</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>101138275.69</v>
+        <v>102244861.39</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>66777.09</v>
+        <v>67507.72</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>-564031.21</v>
+        <v>-4078799.42</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>-0.55</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="87">
@@ -6701,22 +7025,22 @@
         </is>
       </c>
       <c r="D87" s="7" t="n">
-        <v>58602445.04</v>
+        <v>52932339.39</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>38692.58</v>
+        <v>34948.86</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>57349876.28</v>
+        <v>54512793.16</v>
       </c>
       <c r="G87" s="8" t="n">
-        <v>37865.56</v>
+        <v>35992.36</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>-1252568.76</v>
+        <v>1580453.77</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-2.14</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="88">
@@ -6736,22 +7060,22 @@
         </is>
       </c>
       <c r="D88" s="7" t="n">
-        <v>24148139.83</v>
+        <v>27896773.21</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>15943.94</v>
+        <v>18418.99</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>25011546.35</v>
+        <v>28613455.17</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>16514.01</v>
+        <v>18892.19</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>863406.52</v>
+        <v>716681.96</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>3.58</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="89">
@@ -6771,22 +7095,22 @@
         </is>
       </c>
       <c r="D89" s="7" t="n">
-        <v>18395134.33</v>
+        <v>18359209.56</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>12145.49</v>
+        <v>12121.77</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>18776853.06</v>
+        <v>19118613.07</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>12397.52</v>
+        <v>12623.17</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>381718.73</v>
+        <v>759403.51</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>2.08</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="90">
@@ -6806,22 +7130,22 @@
         </is>
       </c>
       <c r="D90" s="7" t="n">
-        <v>110346907.96</v>
+        <v>106598572.73</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>72857.14</v>
+        <v>70382.28</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>110315463.83</v>
+        <v>102848652.28</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>72836.38</v>
+        <v>67906.37</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>-31444.13</v>
+        <v>-3749920.45</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>-0.03</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="91">
@@ -6841,22 +7165,22 @@
         </is>
       </c>
       <c r="D91" s="7" t="n">
-        <v>63356154.6</v>
+        <v>56332708.02</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>41831.24</v>
+        <v>37193.97</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>61197593.74</v>
+        <v>53772050.53</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>40406.04</v>
+        <v>35503.28</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>-2158560.87</v>
+        <v>-2560657.49</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-3.41</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="92">
@@ -6876,22 +7200,22 @@
         </is>
       </c>
       <c r="D92" s="7" t="n">
-        <v>26903823.8</v>
+        <v>24027541.31</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>17763.39</v>
+        <v>15864.31</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>27858152.95</v>
+        <v>23303339.42</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>18393.49</v>
+        <v>15386.15</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>954329.15</v>
+        <v>-724201.89</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>3.55</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="93">
@@ -6911,22 +7235,22 @@
         </is>
       </c>
       <c r="D93" s="7" t="n">
-        <v>22239320.06</v>
+        <v>26756296.32</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>14683.63</v>
+        <v>17665.99</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>21259717.14</v>
+        <v>25773262.33</v>
       </c>
       <c r="G93" s="8" t="n">
-        <v>14036.84</v>
+        <v>17016.93</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>-979602.91</v>
+        <v>-983033.99</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-4.4</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="94">
@@ -6946,22 +7270,22 @@
         </is>
       </c>
       <c r="D94" s="7" t="n">
-        <v>113444821.03</v>
+        <v>119827751</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>74902.55</v>
+        <v>79116.92</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>109183526.49</v>
+        <v>115618497.41</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>72089.00999999999</v>
+        <v>76337.73</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>-4261294.53</v>
+        <v>-4209253.59</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>-3.76</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="95">
@@ -6981,22 +7305,22 @@
         </is>
       </c>
       <c r="D95" s="7" t="n">
-        <v>56521007.62</v>
+        <v>65009469.03</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>37318.3</v>
+        <v>42922.85</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>57992775.25</v>
+        <v>63050188.72</v>
       </c>
       <c r="G95" s="8" t="n">
-        <v>38290.04</v>
+        <v>41629.23</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>1471767.63</v>
+        <v>-1959280.31</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>2.6</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="96">
@@ -7016,22 +7340,22 @@
         </is>
       </c>
       <c r="D96" s="7" t="n">
-        <v>28182340.61</v>
+        <v>25273336.65</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>18607.54</v>
+        <v>16686.86</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>27918457.71</v>
+        <v>25876768.11</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>18433.31</v>
+        <v>17085.28</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>-263882.9</v>
+        <v>603431.46</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="97">
@@ -7051,22 +7375,22 @@
         </is>
       </c>
       <c r="D97" s="7" t="n">
-        <v>23550121.69</v>
+        <v>27458587.43</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>15549.09</v>
+        <v>18129.68</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>23272293.54</v>
+        <v>26691540.59</v>
       </c>
       <c r="G97" s="8" t="n">
-        <v>15365.66</v>
+        <v>17623.23</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>-277828.16</v>
+        <v>-767046.84</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-1.18</v>
+        <v>-2.79</v>
       </c>
     </row>
   </sheetData>

--- a/excel/dashboard_financiero.xlsx
+++ b/excel/dashboard_financiero.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ARS 115,6 M (USD 76,3 k)</t>
+          <t>ARS 115,6 MM (USD 76,3 k)</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ARS 26,7 M (USD 17,6 k)</t>
+          <t>ARS 26,7 MM (USD 17,6 k)</t>
         </is>
       </c>
     </row>
@@ -787,14 +787,14 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ARS 19,2 M (USD 12,7 k)</t>
+          <t>ARS 18,3 MM (USD 12,1 k)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Margen EBITDA</t>
+          <t>Margen EBITDA (último mes)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ARS 3,5 M (USD 2,3 k)</t>
+          <t>ARS 2,6 MM (USD 1,7 k)</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>ARS 357,4 M (USD 236,0 k)</t>
+          <t>ARS 341,7 MM (USD 225,6 k)</t>
         </is>
       </c>
     </row>
@@ -1037,16 +1037,16 @@
         <v>-427.64</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>4877503.14</v>
+        <v>4715581.53</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>3220.4</v>
+        <v>3113.49</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>15280195.85</v>
+        <v>14146744.58</v>
       </c>
       <c r="V2" s="8" t="n">
-        <v>10088.83</v>
+        <v>9340.459999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1109,16 +1109,16 @@
         <v>-633.17</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>3524898.99</v>
+        <v>3285153.29</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>2327.33</v>
+        <v>2169.04</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>11533679.77</v>
+        <v>9855459.880000001</v>
       </c>
       <c r="V3" s="8" t="n">
-        <v>7615.17</v>
+        <v>6507.12</v>
       </c>
     </row>
     <row r="4">
@@ -1181,16 +1181,16 @@
         <v>-120.74</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>5557012.23</v>
+        <v>5511296.82</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>3669.05</v>
+        <v>3638.86</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>16853898.33</v>
+        <v>16533890.46</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>11127.88</v>
+        <v>10916.59</v>
       </c>
     </row>
     <row r="5">
@@ -1217,7 +1217,7 @@
         <v>33905.86</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>45187536.69</v>
+        <v>45187536.68</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>29835.31</v>
@@ -1229,7 +1229,7 @@
         <v>16508.52</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>20184299.65</v>
+        <v>20184299.64</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>13326.79</v>
@@ -1241,7 +1241,7 @@
         <v>956.12</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>18736196.96</v>
+        <v>18736196.95</v>
       </c>
       <c r="P5" s="8" t="n">
         <v>12370.67</v>
@@ -1253,16 +1253,16 @@
         <v>-70.19</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>4684049.24</v>
+        <v>4657472.44</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>3092.67</v>
+        <v>3075.12</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>14158454.91</v>
+        <v>13972417.32</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>9348.200000000001</v>
+        <v>9225.360000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1283,7 +1283,7 @@
         <v>64929.39</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>54613597.64</v>
+        <v>54613597.63</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>36058.92</v>
@@ -1325,16 +1325,16 @@
         <v>-770.71</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>3960100.67</v>
+        <v>3668276.67</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>2614.68</v>
+        <v>2422</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>13047597.98</v>
+        <v>11004830.01</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>8614.75</v>
+        <v>7266</v>
       </c>
     </row>
     <row r="7">
@@ -1385,7 +1385,7 @@
         <v>996.4400000000001</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>18381422.66</v>
+        <v>18381422.67</v>
       </c>
       <c r="P7" s="8" t="n">
         <v>12136.43</v>
@@ -1397,16 +1397,16 @@
         <v>-590.58</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>4595355.67</v>
+        <v>4371735.77</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>3034.11</v>
+        <v>2886.46</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>14680546.58</v>
+        <v>13115207.31</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>9692.91</v>
+        <v>8659.389999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1445,7 +1445,7 @@
         <v>14539.3</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>22867597.96</v>
+        <v>22867597.95</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>15098.45</v>
@@ -1469,16 +1469,16 @@
         <v>-648.8099999999999</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>5350806.39</v>
+        <v>5105141.51</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>3532.9</v>
+        <v>3370.7</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>17035078.7</v>
+        <v>15315424.53</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>11247.5</v>
+        <v>10112.09</v>
       </c>
     </row>
     <row r="9">
@@ -1499,7 +1499,7 @@
         <v>61052.79</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>51433132.39</v>
+        <v>51433132.38</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>33959</v>
@@ -1517,7 +1517,7 @@
         <v>16388.26</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16214226.91</v>
+        <v>16214226.92</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>10705.53</v>
@@ -1541,16 +1541,16 @@
         <v>158.41</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>3706800.03</v>
+        <v>3766780.52</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>2447.43</v>
+        <v>2487.04</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>10880478.13</v>
+        <v>11300341.55</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>7183.89</v>
+        <v>7461.11</v>
       </c>
     </row>
     <row r="10">
@@ -1571,7 +1571,7 @@
         <v>57697.78</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>50543534.83</v>
+        <v>50543534.84</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>33371.64</v>
@@ -1613,16 +1613,16 @@
         <v>-55.34</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>3580706.45</v>
+        <v>3559751.31</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>2364.18</v>
+        <v>2350.34</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>10825939.92</v>
+        <v>10679253.94</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>7147.88</v>
+        <v>7051.03</v>
       </c>
     </row>
     <row r="11">
@@ -1643,7 +1643,7 @@
         <v>58900.12</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>49698821.97</v>
+        <v>49698821.98</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>32813.91</v>
@@ -1673,7 +1673,7 @@
         <v>883.5</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>13933089.73</v>
+        <v>13933089.72</v>
       </c>
       <c r="P11" s="8" t="n">
         <v>9199.4</v>
@@ -1685,16 +1685,16 @@
         <v>-26.68</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>3483272.43</v>
+        <v>3473170.57</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>2299.85</v>
+        <v>2293.18</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>10490224.73</v>
+        <v>10419511.71</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>6926.23</v>
+        <v>6879.54</v>
       </c>
     </row>
     <row r="12">
@@ -1715,7 +1715,7 @@
         <v>60312.62</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>47751811.92</v>
+        <v>47751811.93</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>31528.39</v>
@@ -1733,7 +1733,7 @@
         <v>14093.49</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>22250096.36</v>
+        <v>22250096.35</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>14690.75</v>
@@ -1745,7 +1745,7 @@
         <v>904.6900000000001</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>20879885.14</v>
+        <v>20879885.13</v>
       </c>
       <c r="P12" s="8" t="n">
         <v>13786.06</v>
@@ -1757,16 +1757,16 @@
         <v>-374.68</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>5219971.28</v>
+        <v>5078103.25</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>3446.51</v>
+        <v>3352.84</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>16227385.98</v>
+        <v>15234309.75</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>10714.22</v>
+        <v>10058.53</v>
       </c>
     </row>
     <row r="13">
@@ -1817,7 +1817,7 @@
         <v>916.13</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>20810494.45</v>
+        <v>20810494.46</v>
       </c>
       <c r="P13" s="8" t="n">
         <v>13740.24</v>
@@ -1829,16 +1829,16 @@
         <v>-393.36</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>5202623.61</v>
+        <v>5053682.53</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>3435.06</v>
+        <v>3336.72</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>16203635.18</v>
+        <v>15161047.58</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>10698.54</v>
+        <v>10010.16</v>
       </c>
     </row>
     <row r="14">
@@ -1901,16 +1901,16 @@
         <v>-538.76</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>5247585.21</v>
+        <v>5043587.88</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>3464.75</v>
+        <v>3330.06</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>16558744.95</v>
+        <v>15130763.65</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>10933</v>
+        <v>9990.17</v>
       </c>
     </row>
     <row r="15">
@@ -1973,16 +1973,16 @@
         <v>13.16</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>4089432.55</v>
+        <v>4094414</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>2700.07</v>
+        <v>2703.36</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>12248371.82</v>
+        <v>12283242.01</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>8087.05</v>
+        <v>8110.08</v>
       </c>
     </row>
     <row r="16">
@@ -2033,7 +2033,7 @@
         <v>1132.89</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>21899522.03</v>
+        <v>21899522.02</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>14459.28</v>
@@ -2045,16 +2045,16 @@
         <v>-333.14</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>5474880.51</v>
+        <v>5348741.44</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>3614.82</v>
+        <v>3531.54</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>16929197.77</v>
+        <v>16046224.33</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>11177.59</v>
+        <v>10594.61</v>
       </c>
     </row>
     <row r="17">
@@ -2117,16 +2117,16 @@
         <v>140.38</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>5439628.16</v>
+        <v>5492782.33</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>3591.54</v>
+        <v>3626.64</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>16106267.77</v>
+        <v>16478347</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>10634.25</v>
+        <v>10879.92</v>
       </c>
     </row>
     <row r="18">
@@ -2189,16 +2189,16 @@
         <v>-931.1900000000001</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>5733570.89</v>
+        <v>5380983.53</v>
       </c>
       <c r="T18" s="8" t="n">
-        <v>3785.62</v>
+        <v>3552.82</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>18611062.1</v>
+        <v>16142950.58</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>12288.05</v>
+        <v>10658.47</v>
       </c>
     </row>
     <row r="19">
@@ -2219,7 +2219,7 @@
         <v>76545.61</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>62147742.42</v>
+        <v>62147742.41</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>41033.38</v>
@@ -2237,7 +2237,7 @@
         <v>17809.02</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>26812666</v>
+        <v>26812666.01</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>17703.21</v>
@@ -2261,16 +2261,16 @@
         <v>524.96</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>6268416.48</v>
+        <v>6467189.82</v>
       </c>
       <c r="T19" s="8" t="n">
-        <v>4138.76</v>
+        <v>4270</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>18010156.06</v>
+        <v>19401569.46</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>11891.3</v>
+        <v>12809.99</v>
       </c>
     </row>
     <row r="20">
@@ -2291,7 +2291,7 @@
         <v>76542.42</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>62471635.1</v>
+        <v>62471635.09</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>41247.23</v>
@@ -2333,16 +2333,16 @@
         <v>-312.86</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>5413658.89</v>
+        <v>5295198.44</v>
       </c>
       <c r="T20" s="8" t="n">
-        <v>3574.4</v>
+        <v>3496.18</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>16714818.47</v>
+        <v>15885595.33</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>11036.05</v>
+        <v>10488.55</v>
       </c>
     </row>
     <row r="21">
@@ -2375,7 +2375,7 @@
         <v>33095.51</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>26132633.81</v>
+        <v>26132633.82</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>17254.21</v>
@@ -2393,7 +2393,7 @@
         <v>1097.16</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>22330964.03</v>
+        <v>22330964.02</v>
       </c>
       <c r="P21" s="8" t="n">
         <v>14744.14</v>
@@ -2405,16 +2405,16 @@
         <v>-516.9400000000001</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>5582741.01</v>
+        <v>5387004.77</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>3686.03</v>
+        <v>3556.8</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>17531167.95</v>
+        <v>16161014.32</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>11575.05</v>
+        <v>10670.4</v>
       </c>
     </row>
     <row r="22">
@@ -2435,7 +2435,7 @@
         <v>68729.31</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>55770431.19</v>
+        <v>55770431.2</v>
       </c>
       <c r="F22" s="8" t="n">
         <v>36822.73</v>
@@ -2477,16 +2477,16 @@
         <v>409.38</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>5052782.6</v>
+        <v>5207792.04</v>
       </c>
       <c r="T22" s="8" t="n">
-        <v>3336.13</v>
+        <v>3438.47</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>14538310.06</v>
+        <v>15623376.12</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>9599</v>
+        <v>10315.42</v>
       </c>
     </row>
     <row r="23">
@@ -2519,7 +2519,7 @@
         <v>31515.35</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>28613455.17</v>
+        <v>28613455.16</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>18892.19</v>
@@ -2549,16 +2549,16 @@
         <v>-122.15</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>4396235.04</v>
+        <v>4349982.68</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>2902.64</v>
+        <v>2872.1</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>13373714.54</v>
+        <v>13049948.04</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>8830.07</v>
+        <v>8616.299999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2621,16 +2621,16 @@
         <v>37.28</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>6057633.14</v>
+        <v>6071747.08</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>3999.58</v>
+        <v>4008.9</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>18116443.64</v>
+        <v>18215241.24</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>11961.48</v>
+        <v>12026.71</v>
       </c>
     </row>
     <row r="25">
@@ -2651,7 +2651,7 @@
         <v>76337.73</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>63050188.72</v>
+        <v>63050188.71</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>41629.23</v>
@@ -2693,16 +2693,16 @@
         <v>-333.41</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>6239315.78</v>
+        <v>6113071.53</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>4119.54</v>
+        <v>4036.19</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>19222924.35</v>
+        <v>18339214.6</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>12692.04</v>
+        <v>12108.56</v>
       </c>
     </row>
   </sheetData>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>16569417.38</v>
+        <v>15435966.11</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>10940.05</v>
+        <v>10191.68</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>-0</v>
@@ -2844,16 +2844,16 @@
         <v>325.16</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>16357532.89</v>
+        <v>15224081.62</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>10800.15</v>
+        <v>10051.78</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>58357532.89</v>
+        <v>57224081.62</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>38530.87</v>
+        <v>37782.51</v>
       </c>
     </row>
     <row r="3">
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>13391023.24</v>
+        <v>11257314.36</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>8841.49</v>
+        <v>7432.7</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>455488.99</v>
@@ -2892,16 +2892,16 @@
         <v>336.65</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>11761725.93</v>
+        <v>10083506.05</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>7765.74</v>
+        <v>6657.69</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>70119258.81999999</v>
+        <v>67307587.67</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>46296.62</v>
+        <v>44440.2</v>
       </c>
     </row>
     <row r="4">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>15722884.7</v>
+        <v>17982954.3</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>10381.12</v>
+        <v>11873.34</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>-2580077.47</v>
@@ -2940,16 +2940,16 @@
         <v>80.86</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>13820260.77</v>
+        <v>13500252.89</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>9124.9</v>
+        <v>8913.610000000001</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>83939519.59</v>
+        <v>80807840.56</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>55421.52</v>
+        <v>53353.81</v>
       </c>
     </row>
     <row r="5">
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>17199715.22</v>
+        <v>15420520.01</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>11356.2</v>
+        <v>10181.48</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1593157.62</v>
@@ -2988,16 +2988,16 @@
         <v>4009.08</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>21994722.87</v>
+        <v>21808685.28</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>14522.13</v>
+        <v>14399.3</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>105934242.46</v>
+        <v>102616525.84</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>69943.64999999999</v>
+        <v>67753.11</v>
       </c>
     </row>
     <row r="6">
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>13903528.75</v>
+        <v>12479927.16</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>9179.879999999999</v>
+        <v>8239.940000000001</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>-619166.38</v>
@@ -3036,16 +3036,16 @@
         <v>520.16</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>13110054.39</v>
+        <v>11067286.41</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>8655.98</v>
+        <v>7307.24</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>119044296.85</v>
+        <v>113683812.25</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>78599.64</v>
+        <v>75060.35000000001</v>
       </c>
     </row>
     <row r="7">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>10141635.67</v>
+        <v>14624383.35</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>6696.07</v>
+        <v>9655.83</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>-6048086.95</v>
@@ -3084,16 +3084,16 @@
         <v>530.09</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>-998414.76</v>
+        <v>-2563754.03</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>-659.21</v>
+        <v>-1692.73</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>118045882.09</v>
+        <v>111120058.22</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>77940.42999999999</v>
+        <v>73367.61</v>
       </c>
     </row>
     <row r="8">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>24869178.15</v>
+        <v>16779796.92</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>16420.01</v>
+        <v>11078.95</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>6369727.06</v>
@@ -3132,16 +3132,16 @@
         <v>282.55</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>24150646.74</v>
+        <v>22430992.56</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>15945.59</v>
+        <v>14810.18</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>142196528.83</v>
+        <v>133551050.78</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>93886.02</v>
+        <v>88177.8</v>
       </c>
     </row>
     <row r="9">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>15815462</v>
+        <v>12687368.35</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>10442.24</v>
+        <v>8376.9</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>3547957.07</v>
@@ -3180,16 +3180,16 @@
         <v>-4155.58</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>8573820.189999999</v>
+        <v>8993683.6</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>5660.91</v>
+        <v>5938.13</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>150770349.01</v>
+        <v>142544734.38</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>99546.92999999999</v>
+        <v>94115.92999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13004559.73</v>
+        <v>11990059.84</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>8586.33</v>
+        <v>7916.5</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>867813.91</v>
@@ -3228,16 +3228,16 @@
         <v>42.31</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>11675744.73</v>
+        <v>11529058.75</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>7708.97</v>
+        <v>7612.12</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>162446093.74</v>
+        <v>154073793.13</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>107255.91</v>
+        <v>101728.05</v>
       </c>
     </row>
     <row r="11">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>6496513.06</v>
+        <v>11757632.99</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>4289.36</v>
+        <v>7763.04</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>-5331832.95</v>
@@ -3276,16 +3276,16 @@
         <v>16.3</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>5127195.69</v>
+        <v>5056482.67</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>3385.26</v>
+        <v>3338.57</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>167573289.43</v>
+        <v>159130275.8</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>110641.16</v>
+        <v>105066.62</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>14330189.81</v>
+        <v>16604520.97</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>9461.58</v>
+        <v>10963.22</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>-3267407.39</v>
@@ -3324,16 +3324,16 @@
         <v>331.4</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>12803066.24</v>
+        <v>11809990.01</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>8453.290000000001</v>
+        <v>7797.61</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>180376355.67</v>
+        <v>170940265.81</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>119094.46</v>
+        <v>112864.23</v>
       </c>
     </row>
     <row r="13">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>21308592.43</v>
+        <v>16548583.7</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>14069.11</v>
+        <v>10926.29</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>3717421.13</v>
@@ -3372,16 +3372,16 @@
         <v>209.5</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>19336439.67</v>
+        <v>18293852.07</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>12766.99</v>
+        <v>12078.61</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>199712795.35</v>
+        <v>189234117.88</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>131861.44</v>
+        <v>124942.84</v>
       </c>
     </row>
     <row r="14">
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>10898497.31</v>
+        <v>16697992.86</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>7195.79</v>
+        <v>11024.94</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>-7227476.85</v>
@@ -3420,16 +3420,16 @@
         <v>476.46</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>10257255.31</v>
+        <v>8829274.02</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>6772.41</v>
+        <v>5829.58</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>209970050.66</v>
+        <v>198063391.9</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>138633.85</v>
+        <v>130772.42</v>
       </c>
     </row>
     <row r="15">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>15815008.24</v>
+        <v>13919903.17</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>10441.94</v>
+        <v>9190.690000000001</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>1929975.26</v>
@@ -3468,16 +3468,16 @@
         <v>-5.79</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>13151221.7</v>
+        <v>13186091.89</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>8683.16</v>
+        <v>8706.190000000001</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>223121272.36</v>
+        <v>211249483.79</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>147317.02</v>
+        <v>139478.61</v>
       </c>
     </row>
     <row r="16">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>14623249.06</v>
+        <v>17762055.34</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>9655.08</v>
+        <v>11727.49</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>-4021779.72</v>
@@ -3516,16 +3516,16 @@
         <v>6870.51</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>9509835.449999999</v>
+        <v>8626862.01</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>6278.92</v>
+        <v>5695.93</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>232631107.81</v>
+        <v>219876345.8</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>153595.94</v>
+        <v>145174.54</v>
       </c>
     </row>
     <row r="17">
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>13868365.99</v>
+        <v>18362929.4</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>9156.66</v>
+        <v>12124.22</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>-4122484.18</v>
@@ -3564,16 +3564,16 @@
         <v>-77.20999999999999</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>11311680.19</v>
+        <v>11683759.42</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>7468.6</v>
+        <v>7714.26</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>243942788</v>
+        <v>231560105.22</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>161064.54</v>
+        <v>152888.8</v>
       </c>
     </row>
     <row r="18">
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>12625830.83</v>
+        <v>18005536.48</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>8336.27</v>
+        <v>11888.25</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>-7847817.17</v>
@@ -3612,16 +3612,16 @@
         <v>807</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>12294882.68</v>
+        <v>9826771.17</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>8117.76</v>
+        <v>6488.18</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>256237670.69</v>
+        <v>241386876.39</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>169182.3</v>
+        <v>159376.98</v>
       </c>
     </row>
     <row r="19">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>28928239.51</v>
+        <v>21140569.56</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>19100.03</v>
+        <v>13958.17</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>9179083.35</v>
@@ -3660,16 +3660,16 @@
         <v>-212.04</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>26390725.19</v>
+        <v>27782138.59</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>17424.62</v>
+        <v>18343.31</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>282628395.88</v>
+        <v>269169014.98</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>186606.92</v>
+        <v>177720.29</v>
       </c>
     </row>
     <row r="20">
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>23748753.84</v>
+        <v>17624523.03</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>15680.24</v>
+        <v>11636.69</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>5295007.67</v>
@@ -3708,16 +3708,16 @@
         <v>219.76</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>22617419.59</v>
+        <v>21788196.45</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>14933.27</v>
+        <v>14385.77</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>305245815.47</v>
+        <v>290957211.43</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>201540.19</v>
+        <v>192106.06</v>
       </c>
     </row>
     <row r="21">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>18517414.01</v>
+        <v>17822741.56</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>12226.22</v>
+        <v>11767.56</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>-675481.1800000001</v>
@@ -3756,16 +3756,16 @@
         <v>278.29</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>13099897.24</v>
+        <v>11729743.61</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>8649.280000000001</v>
+        <v>7744.63</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>318345712.71</v>
+        <v>302686955.04</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>210189.47</v>
+        <v>199850.69</v>
       </c>
     </row>
     <row r="22">
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>16797198.22</v>
+        <v>17184801.85</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>11090.44</v>
+        <v>11346.36</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>697462.4300000001</v>
@@ -3804,16 +3804,16 @@
         <v>-4570.03</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>5476808.86</v>
+        <v>6561874.93</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>3616.09</v>
+        <v>4332.51</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>323822521.58</v>
+        <v>309248829.97</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>213805.56</v>
+        <v>204183.2</v>
       </c>
     </row>
     <row r="23">
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>20622894.01</v>
+        <v>14583620.96</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>13616.38</v>
+        <v>9628.91</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>5715506.55</v>
@@ -3852,16 +3852,16 @@
         <v>101.43</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>18574767.88</v>
+        <v>18251001.39</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>12264.09</v>
+        <v>12050.32</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>342397289.46</v>
+        <v>327499831.36</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>226069.65</v>
+        <v>216233.52</v>
       </c>
     </row>
     <row r="24">
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>12650850.43</v>
+        <v>19757971.02</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>8352.790000000001</v>
+        <v>13045.31</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>-7008322.99</v>
@@ -3900,16 +3900,16 @@
         <v>-32.24</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>11509005.08</v>
+        <v>11607802.69</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>7598.88</v>
+        <v>7664.11</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>353906294.54</v>
+        <v>339107634.05</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>233668.53</v>
+        <v>223897.64</v>
       </c>
     </row>
     <row r="25">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>21133380.14</v>
+        <v>20073492.06</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>13953.43</v>
+        <v>13253.63</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>176178.33</v>
@@ -3948,16 +3948,16 @@
         <v>267.1</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>3518904.3</v>
+        <v>2635194.55</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>2323.38</v>
+        <v>1739.9</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>357425198.85</v>
+        <v>341742828.6</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>235991.91</v>
+        <v>225637.54</v>
       </c>
     </row>
   </sheetData>
@@ -4575,13 +4575,13 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>20156022.38</v>
+        <v>20156022.37</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>13308.12</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>20184299.65</v>
+        <v>20184299.64</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>13326.79</v>
@@ -4645,19 +4645,19 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>56647588.47</v>
+        <v>56647588.45</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>37401.87</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>54613597.64</v>
+        <v>54613597.63</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>36058.92</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-2033990.83</v>
+        <v>-2033990.82</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>-3.59</v>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>23689997.73</v>
+        <v>23689997.72</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>15641.45</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>22867597.96</v>
+        <v>22867597.95</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>15098.45</v>
@@ -5065,13 +5065,13 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>51292570.92</v>
+        <v>51292570.91</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>33866.2</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>51433132.39</v>
+        <v>51433132.38</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>33959</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>16712809.52</v>
+        <v>16712809.53</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>11034.72</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>16214226.91</v>
+        <v>16214226.92</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>10705.53</v>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>52990676.95</v>
+        <v>52990676.96</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>34987.38</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>50543534.83</v>
+        <v>50543534.84</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>33371.64</v>
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>48455389.49</v>
+        <v>48455389.5</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>31992.93</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>49698821.97</v>
+        <v>49698821.98</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>32813.91</v>
@@ -5485,13 +5485,13 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>49416897.23</v>
+        <v>49416897.24</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>32627.77</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>47751811.92</v>
+        <v>47751811.93</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>31528.39</v>
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>22218147.73</v>
+        <v>22218147.72</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>14669.65</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>22250096.36</v>
+        <v>22250096.35</v>
       </c>
       <c r="G45" s="8" t="n">
         <v>14690.75</v>
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="D71" s="7" t="n">
-        <v>60900926.66</v>
+        <v>60900926.65</v>
       </c>
       <c r="E71" s="8" t="n">
         <v>40210.16</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>62147742.42</v>
+        <v>62147742.41</v>
       </c>
       <c r="G71" s="8" t="n">
         <v>41033.38</v>
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="D73" s="7" t="n">
-        <v>27989554.36</v>
+        <v>27989554.37</v>
       </c>
       <c r="E73" s="8" t="n">
         <v>18480.25</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>26812666</v>
+        <v>26812666.01</v>
       </c>
       <c r="G73" s="8" t="n">
         <v>17703.21</v>
@@ -6605,13 +6605,13 @@
         </is>
       </c>
       <c r="D75" s="7" t="n">
-        <v>60619959.05</v>
+        <v>60619959.04</v>
       </c>
       <c r="E75" s="8" t="n">
         <v>40024.65</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>62471635.1</v>
+        <v>62471635.09</v>
       </c>
       <c r="G75" s="8" t="n">
         <v>41247.23</v>
@@ -6780,13 +6780,13 @@
         </is>
       </c>
       <c r="D80" s="7" t="n">
-        <v>26490947.18</v>
+        <v>26490947.19</v>
       </c>
       <c r="E80" s="8" t="n">
         <v>17490.79</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>26132633.81</v>
+        <v>26132633.82</v>
       </c>
       <c r="G80" s="8" t="n">
         <v>17254.21</v>
@@ -6885,13 +6885,13 @@
         </is>
       </c>
       <c r="D83" s="7" t="n">
-        <v>56024690.2</v>
+        <v>56024690.21</v>
       </c>
       <c r="E83" s="8" t="n">
         <v>36990.6</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>55770431.19</v>
+        <v>55770431.2</v>
       </c>
       <c r="G83" s="8" t="n">
         <v>36822.73</v>
@@ -7060,13 +7060,13 @@
         </is>
       </c>
       <c r="D88" s="7" t="n">
-        <v>27896773.21</v>
+        <v>27896773.2</v>
       </c>
       <c r="E88" s="8" t="n">
         <v>18418.99</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>28613455.17</v>
+        <v>28613455.16</v>
       </c>
       <c r="G88" s="8" t="n">
         <v>18892.19</v>
@@ -7305,13 +7305,13 @@
         </is>
       </c>
       <c r="D95" s="7" t="n">
-        <v>65009469.03</v>
+        <v>65009469.02</v>
       </c>
       <c r="E95" s="8" t="n">
         <v>42922.85</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>63050188.72</v>
+        <v>63050188.71</v>
       </c>
       <c r="G95" s="8" t="n">
         <v>41629.23</v>
